--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="129">
   <si>
     <t>As a</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>I want to</t>
-  </si>
-  <si>
-    <t>owner/ renter</t>
   </si>
   <si>
     <t>unlogged-in owner/ renter</t>
@@ -408,9 +405,6 @@
       </rPr>
       <t xml:space="preserve"> screen itself</t>
     </r>
-  </si>
-  <si>
-    <t>I can list or rent bike(s)</t>
   </si>
   <si>
     <r>
@@ -2648,6 +2642,12 @@
       </rPr>
       <t xml:space="preserve"> screen itself and see respective error messages</t>
     </r>
+  </si>
+  <si>
+    <t>I can list or rent bike(s) or use other features of the Micro2Move app</t>
+  </si>
+  <si>
+    <t>owner/ renter/ logged-in user/ un-logged-in user</t>
   </si>
 </sst>
 </file>
@@ -2737,7 +2737,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2769,12 +2769,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2823,6 +2832,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3114,7 +3129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.1328125" style="9" customWidth="1"/>
@@ -3136,7 +3151,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>4</v>
@@ -3147,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -3166,52 +3181,52 @@
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
     </row>
-    <row r="3" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A4" s="7"/>
       <c r="B4" s="1"/>
       <c r="C4" s="7">
         <v>1.2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
@@ -3221,22 +3236,22 @@
         <v>1.3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
@@ -3246,25 +3261,25 @@
         <v>1.4</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="128.25" x14ac:dyDescent="0.45">
@@ -3275,19 +3290,19 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
@@ -3298,13 +3313,13 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
@@ -3314,22 +3329,22 @@
         <v>1.5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
@@ -3339,25 +3354,25 @@
         <v>1.6</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
@@ -3367,115 +3382,104 @@
         <v>1.7</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
       <c r="B12" s="1"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="H12" s="3"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="7"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="7">
-        <v>1.8</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="C13" s="7"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A14" s="7"/>
       <c r="B14" s="1"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>127</v>
-      </c>
+      <c r="D14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A15" s="7"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="C15" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" s="7"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="7"/>
@@ -3483,25 +3487,35 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A18" s="7"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="C18" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="G18" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
       <c r="B19" s="1"/>
       <c r="C19" s="7"/>
@@ -3509,13 +3523,11 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
       <c r="B20" s="1"/>
       <c r="C20" s="7"/>
@@ -3523,10 +3535,10 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
@@ -3537,239 +3549,235 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="57" x14ac:dyDescent="0.45">
       <c r="A22" s="7"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="7">
-        <v>1.9</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A23" s="7"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="C24" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="G24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A25" s="7"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A26" s="7"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+      <c r="A27" s="8">
+        <v>2</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="57" x14ac:dyDescent="0.45">
-      <c r="A25" s="8">
-        <v>2</v>
-      </c>
-      <c r="B25" s="4" t="s">
+      <c r="E27" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="8">
-        <v>2.1</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A26" s="8"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="A27" s="8"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="8">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A28" s="8"/>
       <c r="B28" s="4"/>
-      <c r="C28" s="8">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>71</v>
-      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="F28" s="4"/>
       <c r="G28" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+        <v>75</v>
+      </c>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A29" s="8"/>
       <c r="B29" s="4"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="C29" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="G29" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="4"/>
-    </row>
-    <row r="30" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A30" s="8"/>
       <c r="B30" s="4"/>
       <c r="C30" s="8">
-        <v>2.4</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="H30" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="57" x14ac:dyDescent="0.45">
       <c r="A31" s="8"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>85</v>
-      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
       <c r="G31" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A32" s="8"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+      <c r="C32" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="G32" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+        <v>84</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A33" s="8"/>
       <c r="B33" s="4"/>
       <c r="C33" s="8">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A34" s="8"/>
       <c r="B34" s="4"/>
       <c r="C34" s="8"/>
@@ -3777,47 +3785,45 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A35" s="8"/>
       <c r="B35" s="4"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="C35" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="G35" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A36" s="8"/>
       <c r="B36" s="4"/>
-      <c r="C36" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>91</v>
-      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
       <c r="G36" s="4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="57" x14ac:dyDescent="0.45">
       <c r="A37" s="8"/>
       <c r="B37" s="4"/>
       <c r="C37" s="8"/>
@@ -3825,23 +3831,33 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A38" s="8"/>
       <c r="B38" s="4"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="C38" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="G38" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+        <v>90</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A39" s="8"/>
       <c r="B39" s="4"/>
       <c r="C39" s="8"/>
@@ -3849,159 +3865,163 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A40" s="8"/>
       <c r="B40" s="4"/>
       <c r="C40" s="8"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H40" s="12"/>
-    </row>
-    <row r="41" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="G40" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:8" ht="57" x14ac:dyDescent="0.45">
       <c r="A41" s="8"/>
       <c r="B41" s="4"/>
       <c r="C41" s="8"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H41" s="12"/>
-    </row>
-    <row r="42" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="G41" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="57" x14ac:dyDescent="0.45">
       <c r="A42" s="8"/>
       <c r="B42" s="4"/>
-      <c r="C42" s="8">
+      <c r="C42" s="8"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A43" s="8"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A44" s="8"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="8">
         <v>2.8</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G42" s="4" t="s">
+      <c r="D44" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H42" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="57" x14ac:dyDescent="0.45">
-      <c r="A43" s="13">
+      <c r="F44" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="57" x14ac:dyDescent="0.45">
+      <c r="A45" s="13">
         <v>3</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="13">
+      <c r="B45" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="13">
         <v>3.1</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E45" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H45" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A44" s="13"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" spans="1:8" ht="57" x14ac:dyDescent="0.45">
-      <c r="A45" s="13"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="46" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A46" s="13"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>114</v>
-      </c>
+      <c r="C46" s="13"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8" ht="57" x14ac:dyDescent="0.45">
       <c r="A47" s="13"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="13">
-        <v>3.3</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>3</v>
-      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="G47" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="H47" s="5"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A48" s="13"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
+      <c r="C48" s="13">
+        <v>3.2</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" s="13"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="5"/>
+      <c r="C49" s="13">
+        <v>3.3</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -4016,6 +4036,26 @@
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A51" s="13"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A52" s="13"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4029,42 +4069,48 @@
   <hyperlinks>
     <hyperlink ref="H3" r:id="rId1" display="Wireframes\0010Splash.png"/>
     <hyperlink ref="H4" r:id="rId2" display="Wireframes\0020Landing.png"/>
-    <hyperlink ref="H11" r:id="rId3" display="Wireframes\0090ExploreMaps.png"/>
-    <hyperlink ref="H16" r:id="rId4" display="Wireframes\0040SignUp.png"/>
-    <hyperlink ref="H22" r:id="rId5" display="Wireframes\0042SignUpT&amp;C.png"/>
-    <hyperlink ref="H18" r:id="rId6" display="Wireframes\0043SignUpPhotoIDUpload.png"/>
-    <hyperlink ref="H19" r:id="rId7" display="Wireframes\0044SignUpSelfieCapture.png"/>
-    <hyperlink ref="H20" r:id="rId8" display="Wireframes\0041SignUpErrors.png"/>
-    <hyperlink ref="H21" r:id="rId9" display="Wireframes\0041SignUpErrors.png"/>
-    <hyperlink ref="H23" r:id="rId10" display="Wireframes\0070RenterE-BikeBookingFilter.png"/>
-    <hyperlink ref="H24" r:id="rId11" display="Wireframes\0050OwnerE-BikeListing.png"/>
-    <hyperlink ref="H28" r:id="rId12" display="Wireframes\0052OwnerE-BikeListing-Form.png"/>
-    <hyperlink ref="H27" r:id="rId13" display="Wireframes\0051OwnerExistingE-BikesList.png"/>
-    <hyperlink ref="H30" r:id="rId14" display="Wireframes\0053OwnerE-BikeHealthChecklist.png"/>
-    <hyperlink ref="H36" r:id="rId15" display="Wireframes\0060OwnerEditListedE-Bike.png"/>
-    <hyperlink ref="H39" r:id="rId16" display="Wireframes\0061OwnerEditListedE-BikeCalendar.png"/>
-    <hyperlink ref="H42" r:id="rId17" display="Wireframes\0051OwnerExistingE-BikesList.png"/>
-    <hyperlink ref="H34" r:id="rId18" display="Wireframes\0080RenterBookedBikesList.png"/>
-    <hyperlink ref="H43" r:id="rId19" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png"/>
-    <hyperlink ref="H46" r:id="rId20" display="Wireframes\0073RenterE-BikeBookingConfirmation.png"/>
+    <hyperlink ref="I11" r:id="rId3" display="Wireframes\0090ExploreMaps.png"/>
+    <hyperlink ref="H18" r:id="rId4" display="Wireframes\0040SignUp.png"/>
+    <hyperlink ref="H24" r:id="rId5" display="Wireframes\0042SignUpT&amp;C.png"/>
+    <hyperlink ref="H20" r:id="rId6" display="Wireframes\0043SignUpPhotoIDUpload.png"/>
+    <hyperlink ref="H21" r:id="rId7" display="Wireframes\0044SignUpSelfieCapture.png"/>
+    <hyperlink ref="H22" r:id="rId8" display="Wireframes\0041SignUpErrors.png"/>
+    <hyperlink ref="H23" r:id="rId9" display="Wireframes\0041SignUpErrors.png"/>
+    <hyperlink ref="H25" r:id="rId10" display="Wireframes\0070RenterE-BikeBookingFilter.png"/>
+    <hyperlink ref="H26" r:id="rId11" display="Wireframes\0050OwnerE-BikeListing.png"/>
+    <hyperlink ref="H30" r:id="rId12" display="Wireframes\0052OwnerE-BikeListing-Form.png"/>
+    <hyperlink ref="H29" r:id="rId13" display="Wireframes\0051OwnerExistingE-BikesList.png"/>
+    <hyperlink ref="H32" r:id="rId14" display="Wireframes\0053OwnerE-BikeHealthChecklist.png"/>
+    <hyperlink ref="H38" r:id="rId15" display="Wireframes\0060OwnerEditListedE-Bike.png"/>
+    <hyperlink ref="H41" r:id="rId16" display="Wireframes\0061OwnerEditListedE-BikeCalendar.png"/>
+    <hyperlink ref="H44" r:id="rId17" display="Wireframes\0051OwnerExistingE-BikesList.png"/>
+    <hyperlink ref="H36" r:id="rId18" display="Wireframes\0080RenterBookedBikesList.png"/>
+    <hyperlink ref="H45" r:id="rId19" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png"/>
+    <hyperlink ref="H48" r:id="rId20" display="Wireframes\0073RenterE-BikeBookingConfirmation.png"/>
     <hyperlink ref="H5" r:id="rId21" display="Wireframes\0020Landing.png"/>
-    <hyperlink ref="J6" r:id="rId22" display="Wireframes\0020Landing.png"/>
-    <hyperlink ref="J7" r:id="rId23" display="Wireframes\0020Landing.png"/>
-    <hyperlink ref="H6" r:id="rId24" display="Wireframes\0030SignIn.png"/>
-    <hyperlink ref="H7" r:id="rId25" display="Wireframes\0030SignIn.png"/>
-    <hyperlink ref="I8" r:id="rId26" display="Wireframes\0031SignInErrors.png"/>
-    <hyperlink ref="I5" r:id="rId27" display="Wireframes\0030SignIn.png"/>
-    <hyperlink ref="I9" r:id="rId28" display="Wireframes\0070RenterE-BikeBookingFilter.png"/>
-    <hyperlink ref="H8" r:id="rId29" display="Wireframes\0030SignIn.png"/>
-    <hyperlink ref="I10" r:id="rId30" display="Wireframes\0050OwnerE-BikeListing.png"/>
-    <hyperlink ref="J10" r:id="rId31" display="Wireframes\0090ExploreMaps.png"/>
-    <hyperlink ref="I13" r:id="rId32" display="Wireframes\0030SignIn.png"/>
-    <hyperlink ref="H13" r:id="rId33" display="Wireframes\ExploreBottomNavTab.png"/>
-    <hyperlink ref="H14" r:id="rId34" display="Wireframes\ExploreBottomNavTab.png"/>
-    <hyperlink ref="H15" r:id="rId35" display="Wireframes\0031SignInErrors.png"/>
-    <hyperlink ref="H12" r:id="rId36" display="Wireframes\ExploreBottomNavTab.png"/>
+    <hyperlink ref="H6" r:id="rId22" display="Wireframes\0030SignIn.png"/>
+    <hyperlink ref="H7" r:id="rId23" display="Wireframes\0030SignIn.png"/>
+    <hyperlink ref="I8" r:id="rId24" display="Wireframes\0031SignInErrors.png"/>
+    <hyperlink ref="I5" r:id="rId25" display="Wireframes\0030SignIn.png"/>
+    <hyperlink ref="I9" r:id="rId26" display="Wireframes\0070RenterE-BikeBookingFilter.png"/>
+    <hyperlink ref="H8" r:id="rId27" display="Wireframes\0030SignIn.png"/>
+    <hyperlink ref="I10" r:id="rId28" display="Wireframes\0050OwnerE-BikeListing.png"/>
+    <hyperlink ref="I15" r:id="rId29" display="Wireframes\0030SignIn.png"/>
+    <hyperlink ref="H15" r:id="rId30" display="Wireframes\ExploreBottomNavTab.png"/>
+    <hyperlink ref="H16" r:id="rId31" display="Wireframes\ExploreBottomNavTab.png"/>
+    <hyperlink ref="H17" r:id="rId32" display="Wireframes\0031SignInErrors.png"/>
+    <hyperlink ref="H14" r:id="rId33" display="Wireframes\ExploreBottomNavTab.png"/>
+    <hyperlink ref="I6" r:id="rId34" display="Wireframes\0020Landing.png"/>
+    <hyperlink ref="J6" r:id="rId35" display="Wireframes\0070RenterE-BikeBookingFilter.png"/>
+    <hyperlink ref="I7" r:id="rId36" display="Wireframes\0020Landing.png"/>
+    <hyperlink ref="J7" r:id="rId37" display="Wireframes\0050OwnerE-BikeListing.png"/>
+    <hyperlink ref="K7" r:id="rId38" display="Wireframes\0051OwnerExistingE-BikesList.png"/>
+    <hyperlink ref="H9" r:id="rId39" display="Wireframes\0020Landing.png"/>
+    <hyperlink ref="H10" r:id="rId40" display="Wireframes\0020Landing.png"/>
+    <hyperlink ref="J10" r:id="rId41" display="Wireframes\0051OwnerExistingE-BikesList.png"/>
+    <hyperlink ref="H11" r:id="rId42" display="Wireframes\0020Landing.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId37"/>
+  <pageSetup orientation="portrait" r:id="rId43"/>
 </worksheet>
 </file>
--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1960535B-5FC1-4A0C-928E-E589DDDAC814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA4466E-FB67-40C2-85F3-2FE2260D9A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8316" yWindow="0" windowWidth="14820" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="19200" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="201">
   <si>
     <t>As a</t>
   </si>
@@ -1301,6 +1301,1354 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">I must NOT be able to check the box for confirming that all features of my e-Bike are working fine in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Listing Form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if any of the features are checked OFF in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Health Checklist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to check the box for confirming that all features of my e-Bike are working fine in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Listing Form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> only if all features are checked ON in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Health Checklist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Your First E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Listing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">List Another E-Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Owner Existing E-Bikes List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press any of my listed </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e-bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner Existing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">e-bikes List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view and edit the E-Bike</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner Edit Listed E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen must open</t>
+    </r>
+  </si>
+  <si>
+    <t>0060OwnerEditListedE-Bike.png</t>
+  </si>
+  <si>
+    <t>I must be able to edit/ upload new the Image of my e-bike</t>
+  </si>
+  <si>
+    <t>I must be able to edit the e-bike name and set another unique name to the same e-bike</t>
+  </si>
+  <si>
+    <t>0061OwnerEditListedE-BikeCalendar.png</t>
+  </si>
+  <si>
+    <t>I can save the changes made to a listed E-Bike</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to view the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner Existing E-Bikes List</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen with the updated E-bike being listed with the updated (changed) details</t>
+    </r>
+  </si>
+  <si>
+    <t>I must be able to change the from and to dates of my e-bike provided there is no open booking for my e-bike before the new start date or after the new end date</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Save Changes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner Edit Listed e-bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List My E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Listing Form</t>
+    </r>
+  </si>
+  <si>
+    <t>my e-bike is listed in the App.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If all the mandatory details are filled up my e-bike should be listed and viewable in my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerExistingE-BikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If all the mandatory details are filled up my e-bike should be listed and viewable by all Renters in their </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedBikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screens</t>
+    </r>
+  </si>
+  <si>
+    <t>0080RenterBookedBikesList.png</t>
+  </si>
+  <si>
+    <t>I can view available e-bikes for rent in the Micro2Move App matching my filters</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">enter some or all filter fields in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen and press </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Continue</t>
+    </r>
+  </si>
+  <si>
+    <t>0072RenterE-BikeBooking-BikeDetails.png</t>
+  </si>
+  <si>
+    <t>If no Matching e-bikes are found, I must see a proper message.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book This Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBooking-BikeDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> any of the bikes listed in the same screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view the details of the same bike.</t>
+  </si>
+  <si>
+    <t>0073RenterE-BikeBookingConfirmation.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can view the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Listing Form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav tab </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Your First E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Listing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If my credentials are valid and I have started from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rent a Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Landing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Screen, I must be logged in into my account in Micro2Move app and subsequently landing on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Renter E-BikeBooking Filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen (with a personalized welcome note on top) on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">My Rides </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bottom navigation tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If my credentials are valid and I have started from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List a Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Landing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Screen, I must be logged in into my account in Micro2Move app and subsequently landing on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Owner E-Bike Listing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(In case I have no bikes listed)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">/ Owner Existing E-Bikes List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(In case I have one or more bikes listed) screen (with a personalized welcome note on top) on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottom navigation tab</t>
+    </r>
+  </si>
+  <si>
+    <t>un-logged-in user</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Or the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav Tabs, while I am on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav Tab</t>
+    </r>
+  </si>
+  <si>
+    <t>ExploreBottomNavTab.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be landing on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sign In </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen.</t>
+    </r>
+  </si>
+  <si>
+    <t>On Successful submission of valid credential, I must land on the respective Bottom Nav Tab</t>
+  </si>
+  <si>
+    <t>I can list or rent bike(s) or use other features of the Micro2Move app</t>
+  </si>
+  <si>
+    <t>owner/ renter/ logged-in user/ un-logged-in user</t>
+  </si>
+  <si>
+    <t>logged-in user</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can visit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Or the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tabs</t>
+    </r>
+  </si>
+  <si>
+    <t>I must be landing on the respective tab</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> My Bikes, Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Or the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav Tabs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can visit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes, Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Or the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tabs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If I press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Continue </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button and my registration details are invalid I must see respective error messages on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>User</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Registration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen itself</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">I must be able to visit details </t>
     </r>
     <r>
@@ -1312,6 +2660,326 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>Terms and Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> link, scroll up to see all the details and navigate back by clicking </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button</t>
+    </r>
+  </si>
+  <si>
+    <t>unregistered renter</t>
+  </si>
+  <si>
+    <t>unregistered owner</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On submission of invalid credential, I must see respective error messages on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SignIn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">owner with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>existing listed bikes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">owner with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no listed bikes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Another E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerExistingE-BikesList.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can view the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerE-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Listing-Form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav tab </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to view a welcome message with my name, the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Your First E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> big button and a list of benefits of listing my bike in this screen on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to view a welcome message with my name, my previously listed bikes and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Another E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button in this screen on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to visit details of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Owner E-Bike Health Checklist </t>
     </r>
     <r>
@@ -1348,7 +3016,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">I must NOT be able to check the box for confirming that all features of my e-Bike are working fine in the </t>
+      <t xml:space="preserve">If all mandatory and legit details are not provided in the </t>
     </r>
     <r>
       <rPr>
@@ -1369,91 +3037,78 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> if any of the features are checked OFF in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike Health Checklist</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to check the box for confirming that all features of my e-Bike are working fine in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike Listing Form</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> only if all features are checked ON in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike Health Checklist</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List Your First E-Bike</t>
+      <t>, the same form/ screen must reappear back with respective error messages.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to view the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen with the details of the e-bike selected by me.</t>
+    </r>
+  </si>
+  <si>
+    <t>If one or more bikes are found matching my filters, the first bike must be showed on top with larger image and details. The rest of the bikes must be showed as a list.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see a list of matching e-bikes in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBooking-BikeDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sorted in ascending order of price.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
     </r>
     <r>
       <rPr>
@@ -1474,49 +3129,270 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Owner E-Bike Listing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">OR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">List Another E-Bike </t>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view the details of the same bike's owner</t>
+  </si>
+  <si>
+    <t>0075RenterE-BikeBooking-SelectedBike'sOwnerDetails.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must to navigated to view the owner's community activties if I click on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Community Activities </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be navigated back to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeBookingConfirmation </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen if I click on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Learn More </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view the detailed insurance policy</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see the full insurance policy and an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see the owner's name, short bio, number of the e-bikes listed by them so far, rating with the number of raters, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Community Activities</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink and an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button.</t>
+    </r>
+  </si>
+  <si>
+    <t>0074RenterE-BikeBookingInsuranceDetails.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Book </t>
     </r>
     <r>
       <rPr>
@@ -1537,7 +3413,1123 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Owner Existing E-Bikes List </t>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can book my desired e-bike</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If I have checked the checkbox for purchase mandatory insurance and pressed the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button, my bike must be booked and I must be navigated to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterBookedBikesList </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen, where the recently booked e-bike should be shown at the TOP.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">renter with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no booked e-bikes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book Your First E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button</t>
+    </r>
+  </si>
+  <si>
+    <t>I can start booking my desired e-bike</t>
+  </si>
+  <si>
+    <t>Wireframe TBD</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be navigated to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeBookingFilter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen upon pressing the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book Your First E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">renter with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>existing booked e-bikes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book an E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button</t>
+    </r>
+  </si>
+  <si>
+    <t>I can start booking another e-bike</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see a welcome message with my name, a date filter to sort my e-bikes based on booking time, my previously booked bikes with their respective details and a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Book an E-Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">My Rides </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see a welcome message with my name, benefits of booking an e-bike with micro2move and a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Book Your First E-Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <t>Explore</t>
+  </si>
+  <si>
+    <t>Logged in user</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Explore </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bottom nav tab</t>
+    </r>
+  </si>
+  <si>
+    <t>I can browse the explore features on micro2move app</t>
+  </si>
+  <si>
+    <t>0091ExploreMapsNavigation.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to enter address of my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Starting Point</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Destination</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> upon tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bar on map.</t>
+    </r>
+  </si>
+  <si>
+    <t>0092ExploreMapsNavigationFlow.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see the best possible route to my destination on the map upon successfully entering my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Starting Point</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Destination</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, according to real-time updates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see toggles for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Current Charging Stations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Future Charging Stations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dedicated Bike Stations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bike Lane Infrastructure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when I click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">More </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>icon on the map and should reflect the respective information on map upon toggling them on.</t>
+    </r>
+  </si>
+  <si>
+    <t>0093ExploreMapsMoreOptions.png</t>
+  </si>
+  <si>
+    <t>0094ExploreMapsBikeLanes.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Info </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see a map of my locality, a location search bar, an option to see </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>More</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e-bike related information on map, an option for zooming in and out of the map and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Community Update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ask AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlinks.</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view more information on what concerns me about micro2move</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see relevant information about micro2move on the info screen, with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Info </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
+    </r>
+  </si>
+  <si>
+    <t>0100ExploreInfo.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Community Update </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ask AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <t>I can see all the commnity updates</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see community updates (if any) screen, with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Community Updates </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
+    </r>
+  </si>
+  <si>
+    <t>0110ExploreCommunityUpdates.png</t>
+  </si>
+  <si>
+    <t>I can chat with AI about traffic, e-bike routes etc.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see a text field where I can type my prompt and an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ask AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button, with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ask AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
+    </r>
+  </si>
+  <si>
+    <t>0120ExploreAskAI.png</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bottom nav tab</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view and edit my profile's private and public details</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see and edit my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile Picture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, view-only Name,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Email, Number and renter rating of my</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Listed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e-bikes, Number and Owner Rating</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">of my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rented</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e-bikes, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Joining Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Community Activity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In-App Lessons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Logout </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>options.</t>
+    </r>
+  </si>
+  <si>
+    <t>0130Profile.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Community Activity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">option in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">profile </t>
     </r>
     <r>
       <rPr>
@@ -1549,74 +4541,51 @@
       </rPr>
       <t>screen</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press any of my listed </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>e-bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner Existing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">e-bikes List </t>
+  </si>
+  <si>
+    <t>I can view ongoing activities and sign myself up for them.</t>
+  </si>
+  <si>
+    <t>I must be able to view details and sign myself up for the activities listed on the screen.</t>
+  </si>
+  <si>
+    <t>0131ProfileCommunityActivity.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">In-App Lessons </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">option in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">profile </t>
     </r>
     <r>
       <rPr>
@@ -1630,1446 +4599,88 @@
     </r>
   </si>
   <si>
-    <t>I can view and edit the E-Bike</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner Edit Listed E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen must open</t>
-    </r>
-  </si>
-  <si>
-    <t>0060OwnerEditListedE-Bike.png</t>
-  </si>
-  <si>
-    <t>I must be able to edit/ upload new the Image of my e-bike</t>
-  </si>
-  <si>
-    <t>I must be able to edit the e-bike name and set another unique name to the same e-bike</t>
-  </si>
-  <si>
-    <t>0061OwnerEditListedE-BikeCalendar.png</t>
-  </si>
-  <si>
-    <t>I can save the changes made to a listed E-Bike</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to view the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner Existing E-Bikes List</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen with the updated E-bike being listed with the updated (changed) details</t>
-    </r>
-  </si>
-  <si>
-    <t>I must be able to change the from and to dates of my e-bike provided there is no open booking for my e-bike before the new start date or after the new end date</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Save Changes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner Edit Listed e-bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List My E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike Listing Form</t>
-    </r>
-  </si>
-  <si>
-    <t>my e-bike is listed in the App.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If all the mandatory details are filled up my e-bike should be listed and viewable in my </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerExistingE-BikesList</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If all the mandatory details are filled up my e-bike should be listed and viewable by all Renters in their </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterBookedBikesList</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screens</t>
-    </r>
-  </si>
-  <si>
-    <t>0080RenterBookedBikesList.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If all mandatory and legit details are not provided in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike Listing Form</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, the same form/ screen must reappear back with proper error messages.</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view available e-bikes for rent in the Micro2Move App matching my filters</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">enter some or all filter fields in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen and press </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Continue</t>
-    </r>
-  </si>
-  <si>
-    <t>I must be able to see a list of matching e-bikes in the RenterE-BikeBooking-BikeDetails sorted in ascending order of price.</t>
-  </si>
-  <si>
-    <t>0072RenterE-BikeBooking-BikeDetails.png</t>
-  </si>
-  <si>
-    <t>If no Matching e-bikes are found, I must see a proper message.</t>
-  </si>
-  <si>
-    <t>If one or more bikes are found matching my filters, the first bike must be showed on top with larger image and details. The rest of the bikes must be showed as a list</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book This Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBooking-BikeDetails</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> any of the bikes listed in the same screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view the details of the same bike.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to view the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingConfirmation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen with the details of the clicked e-bike</t>
-    </r>
-  </si>
-  <si>
-    <t>0073RenterE-BikeBookingConfirmation.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can view the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Listing Form</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav tab </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List Your First E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike Listing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If my credentials are valid and I have started from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rent a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Landing </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Screen, I must be logged in into my account in Micro2Move app and subsequently landing on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Renter E-BikeBooking Filter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen (with a personalized welcome note on top) on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">My Rides </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bottom navigation tab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If my credentials are valid and I have started from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Landing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Screen, I must be logged in into my account in Micro2Move app and subsequently landing on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Owner E-Bike Listing </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(In case I have no bikes listed)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">/ Owner Existing E-Bikes List </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">(In case I have one or more bikes listed) screen (with a personalized welcome note on top) on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottom navigation tab</t>
-    </r>
-  </si>
-  <si>
-    <t>un-logged-in user</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Or the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav Tabs, while I am on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav Tab</t>
-    </r>
-  </si>
-  <si>
-    <t>ExploreBottomNavTab.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be landing on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Sign In </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen.</t>
-    </r>
-  </si>
-  <si>
-    <t>On Successful submission of valid credential, I must land on the respective Bottom Nav Tab</t>
-  </si>
-  <si>
-    <t>I can list or rent bike(s) or use other features of the Micro2Move app</t>
-  </si>
-  <si>
-    <t>owner/ renter/ logged-in user/ un-logged-in user</t>
-  </si>
-  <si>
-    <t>logged-in user</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can visit </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Or the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tabs</t>
-    </r>
-  </si>
-  <si>
-    <t>I must be landing on the respective tab</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> My Bikes, Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Or the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav Tabs</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can visit </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes, Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Or the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tabs</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If I press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Continue </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">button and my registration details are invalid I must see respective error messages on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>User</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Registration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen itself</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to visit details </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Terms and Conditions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> link, scroll up to see all the details and navigate back by clicking </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button</t>
-    </r>
-  </si>
-  <si>
-    <t>unregistered renter</t>
-  </si>
-  <si>
-    <t>unregistered owner</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">On submission of invalid credential, I must see respective error messages on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SignIn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">owner with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>existing listed bikes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">owner with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>no listed bikes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List Another E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerExistingE-BikesList.png</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can view the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerE-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Listing-Form</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav tab </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to view a welcome message with my name, the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List Your First E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> big button and a list of benefits of listing my bike in this screen on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav tab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to view a welcome message with my name, my previously listed bikes and the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List Another E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button in this screen on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav tab</t>
+    <t>I can view interactive lessons regarding e-bikes, traffic and safety measures.</t>
+  </si>
+  <si>
+    <t>I must be able to view and interact with the lessons listed on the screen.</t>
+  </si>
+  <si>
+    <t>0132ProfileLessons.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Logout </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">option in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can logout from the micro2move app.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be logged out from the app and be redirected to the landing screen upon pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Logout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
     </r>
   </si>
 </sst>
@@ -3116,7 +4727,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3159,8 +4770,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3184,15 +4813,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -3206,7 +4826,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3250,14 +4870,41 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3549,14 +5196,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="9" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="6.33203125" style="9" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.77734375" style="2" customWidth="1"/>
     <col min="7" max="7" width="40.44140625" style="2" customWidth="1"/>
     <col min="8" max="11" width="13.5546875" style="2" customWidth="1"/>
@@ -3564,31 +5211,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -3598,8 +5245,8 @@
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -3612,13 +5259,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>30</v>
@@ -3634,7 +5281,7 @@
         <v>1.2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>27</v>
@@ -3674,7 +5321,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="1"/>
       <c r="C6" s="7">
@@ -3690,7 +5337,7 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>40</v>
@@ -3702,7 +5349,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="161.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="1"/>
       <c r="C7" s="7"/>
@@ -3710,7 +5357,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>40</v>
@@ -3725,7 +5372,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="1"/>
       <c r="C8" s="7"/>
@@ -3742,7 +5389,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="1"/>
       <c r="C9" s="7">
@@ -3767,7 +5414,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="1"/>
       <c r="C10" s="7">
@@ -3835,29 +5482,29 @@
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="1"/>
       <c r="C13" s="7">
         <v>1.8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>40</v>
@@ -3871,10 +5518,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3885,7 +5532,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>47</v>
@@ -3896,22 +5543,22 @@
       <c r="B16" s="1"/>
       <c r="C16" s="7"/>
       <c r="D16" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="10" t="s">
@@ -3933,7 +5580,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="1"/>
       <c r="C18" s="7"/>
@@ -3945,7 +5592,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="1"/>
       <c r="C19" s="7"/>
@@ -3959,7 +5606,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="1"/>
       <c r="C20" s="7"/>
@@ -3973,7 +5620,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="1"/>
       <c r="C21" s="7"/>
@@ -3987,7 +5634,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="1"/>
       <c r="C22" s="7"/>
@@ -3995,13 +5642,13 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="1"/>
       <c r="C23" s="7">
@@ -4017,20 +5664,20 @@
         <v>59</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="1"/>
       <c r="C24" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>21</v>
@@ -4045,12 +5692,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="B25" s="1"/>
       <c r="C25" s="7"/>
       <c r="D25" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>21</v>
@@ -4065,7 +5712,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>2</v>
       </c>
@@ -4076,64 +5723,70 @@
         <v>2.1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="4"/>
       <c r="C27" s="8"/>
       <c r="D27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="8">
+      <c r="I27" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="16"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="16">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="4"/>
       <c r="C29" s="8">
@@ -4143,7 +5796,7 @@
         <v>67</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>73</v>
@@ -4155,7 +5808,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="4"/>
       <c r="C30" s="8"/>
@@ -4167,7 +5820,7 @@
       </c>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="4"/>
       <c r="C31" s="8">
@@ -4183,13 +5836,13 @@
         <v>75</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="4"/>
       <c r="C32" s="8">
@@ -4205,11 +5858,11 @@
         <v>79</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="4"/>
       <c r="C33" s="8"/>
@@ -4217,11 +5870,11 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="4"/>
       <c r="C34" s="8">
@@ -4231,31 +5884,31 @@
         <v>67</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="16"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="H35" s="12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="4"/>
       <c r="C36" s="8"/>
@@ -4263,11 +5916,11 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="4"/>
       <c r="C37" s="8">
@@ -4277,19 +5930,19 @@
         <v>67</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="H37" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="4"/>
       <c r="C38" s="8"/>
@@ -4297,11 +5950,11 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="4"/>
       <c r="C39" s="8"/>
@@ -4309,11 +5962,11 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="4"/>
       <c r="C40" s="8"/>
@@ -4321,13 +5974,13 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="4"/>
       <c r="C41" s="8"/>
@@ -4339,7 +5992,7 @@
       </c>
       <c r="H41" s="12"/>
     </row>
-    <row r="42" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="4"/>
       <c r="C42" s="8"/>
@@ -4351,7 +6004,7 @@
       </c>
       <c r="H42" s="12"/>
     </row>
-    <row r="43" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="4"/>
       <c r="C43" s="8">
@@ -4361,19 +6014,19 @@
         <v>67</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
         <v>3</v>
       </c>
@@ -4387,19 +6040,22 @@
         <v>3</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F44" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I44" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
       <c r="B45" s="5"/>
       <c r="C45" s="13"/>
@@ -4407,11 +6063,11 @@
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="5"/>
       <c r="C46" s="13"/>
@@ -4419,11 +6075,13 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H46" s="5"/>
-    </row>
-    <row r="47" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="5"/>
       <c r="C47" s="13">
@@ -4433,19 +6091,22 @@
         <v>3</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="5"/>
       <c r="C48" s="13">
@@ -4454,40 +6115,390 @@
       <c r="D48" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E48" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="5"/>
       <c r="C49" s="13"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="G49" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="H49" s="5"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="5"/>
       <c r="C50" s="13"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="G50" s="5" t="s">
+        <v>142</v>
+      </c>
       <c r="H50" s="5"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
+      <c r="C51" s="13">
+        <v>3.4</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="13"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="13"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="13"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="13">
+        <v>3.6</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="13"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A56" s="13"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A57" s="20">
+        <v>4</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="20">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="G57" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H57" s="22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="20"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="H58" s="22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="20"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="H59" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="20"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="H60" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="I60" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="20"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="20">
+        <v>4.2</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20">
+        <v>4.3</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="G62" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H62" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="20"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="G63" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="H63" s="23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="24">
+        <v>5</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C64" s="24">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="F64" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="G64" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="H64" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="24"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="24">
+        <v>5.2</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="G65" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" s="26" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="24"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="24">
+        <v>5.3</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="F66" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="G66" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="H66" s="26" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="24"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="24">
+        <v>5.4</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="F67" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="G67" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="H67" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4501,51 +6512,74 @@
   <hyperlinks>
     <hyperlink ref="H3" r:id="rId1" display="Wireframes\0010Splash.png" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="H4" r:id="rId2" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="I11" r:id="rId3" display="Wireframes\0090ExploreMaps.png" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H17" r:id="rId4" display="Wireframes\0040SignUp.png" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H23" r:id="rId5" display="Wireframes\0042SignUpT&amp;C.png" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H19" r:id="rId6" display="Wireframes\0043SignUpPhotoIDUpload.png" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H20" r:id="rId7" display="Wireframes\0044SignUpSelfieCapture.png" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H21" r:id="rId8" display="Wireframes\0041SignUpErrors.png" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="H22" r:id="rId9" display="Wireframes\0041SignUpErrors.png" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H24" r:id="rId10" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="H25" r:id="rId11" display="Wireframes\0050OwnerE-BikeListing.png" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H29" r:id="rId12" display="Wireframes\0052OwnerE-BikeListing-Form.png" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H28" r:id="rId13" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H31" r:id="rId14" display="Wireframes\0053OwnerE-BikeHealthChecklist.png" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H37" r:id="rId15" display="Wireframes\0060OwnerEditListedE-Bike.png" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H40" r:id="rId16" display="Wireframes\0061OwnerEditListedE-BikeCalendar.png" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="H43" r:id="rId17" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="H35" r:id="rId18" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="H44" r:id="rId19" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H47" r:id="rId20" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="H5" r:id="rId21" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H6" r:id="rId22" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="H7" r:id="rId23" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="I8" r:id="rId24" display="Wireframes\0031SignInErrors.png" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="I5" r:id="rId25" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="I9" r:id="rId26" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="H8" r:id="rId27" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="I10" r:id="rId28" display="Wireframes\0050OwnerE-BikeListing.png" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="I13" r:id="rId29" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="H13" r:id="rId30" display="Wireframes\ExploreBottomNavTab.png" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="H14" r:id="rId31" display="Wireframes\ExploreBottomNavTab.png" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="H15" r:id="rId32" display="Wireframes\0031SignInErrors.png" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="H12" r:id="rId33" display="Wireframes\ExploreBottomNavTab.png" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="I6" r:id="rId34" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="J6" r:id="rId35" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="I7" r:id="rId36" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="J7" r:id="rId37" display="Wireframes\0050OwnerE-BikeListing.png" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="K7" r:id="rId38" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="H9" r:id="rId39" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="H10" r:id="rId40" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="J10" r:id="rId41" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="H11" r:id="rId42" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="H16" r:id="rId43" display="Wireframes\ExploreBottomNavTab.png" xr:uid="{FC90D99B-22D7-4F68-9EF8-6181D6513BAA}"/>
-    <hyperlink ref="H26" r:id="rId44" display="Wireframes\0050OwnerE-BikeListing.png" xr:uid="{C7EF654C-CDE9-4C44-9AC8-91E3E6589EDA}"/>
-    <hyperlink ref="H27" r:id="rId45" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{5198BC81-4DEC-491E-91AC-63513529B551}"/>
+    <hyperlink ref="H17" r:id="rId3" display="Wireframes\0040SignUp.png" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H23" r:id="rId4" display="Wireframes\0042SignUpT&amp;C.png" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H19" r:id="rId5" display="Wireframes\0043SignUpPhotoIDUpload.png" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="H20" r:id="rId6" display="Wireframes\0044SignUpSelfieCapture.png" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="H21" r:id="rId7" display="Wireframes\0041SignUpErrors.png" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="H22" r:id="rId8" display="Wireframes\0041SignUpErrors.png" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="H24" r:id="rId9" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H25" r:id="rId10" display="Wireframes\0050OwnerE-BikeListing.png" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="H29" r:id="rId11" display="Wireframes\0052OwnerE-BikeListing-Form.png" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="H28" r:id="rId12" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="H31" r:id="rId13" display="Wireframes\0053OwnerE-BikeHealthChecklist.png" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="H37" r:id="rId14" display="Wireframes\0060OwnerEditListedE-Bike.png" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="H40" r:id="rId15" display="Wireframes\0061OwnerEditListedE-BikeCalendar.png" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="H43" r:id="rId16" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="H35" r:id="rId17" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="H5" r:id="rId18" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="H6" r:id="rId19" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="H7" r:id="rId20" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="I8" r:id="rId21" display="Wireframes\0031SignInErrors.png" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="I5" r:id="rId22" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="I9" r:id="rId23" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="H8" r:id="rId24" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="I10" r:id="rId25" display="Wireframes\0050OwnerE-BikeListing.png" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="I13" r:id="rId26" display="Wireframes\0030SignIn.png" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="H13" r:id="rId27" display="Wireframes\ExploreBottomNavTab.png" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="H14" r:id="rId28" display="Wireframes\ExploreBottomNavTab.png" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="H15" r:id="rId29" display="Wireframes\0031SignInErrors.png" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="H12" r:id="rId30" display="Wireframes\ExploreBottomNavTab.png" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="I6" r:id="rId31" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="J6" r:id="rId32" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="I7" r:id="rId33" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="J7" r:id="rId34" display="Wireframes\0050OwnerE-BikeListing.png" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K7" r:id="rId35" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="H9" r:id="rId36" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="H10" r:id="rId37" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="J10" r:id="rId38" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="H11" r:id="rId39" display="Wireframes\0020Landing.png" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="H16" r:id="rId40" display="Wireframes\ExploreBottomNavTab.png" xr:uid="{FC90D99B-22D7-4F68-9EF8-6181D6513BAA}"/>
+    <hyperlink ref="H26" r:id="rId41" display="Wireframes\0050OwnerE-BikeListing.png" xr:uid="{C7EF654C-CDE9-4C44-9AC8-91E3E6589EDA}"/>
+    <hyperlink ref="H27" r:id="rId42" display="Wireframes\0051OwnerExistingE-BikesList.png" xr:uid="{5198BC81-4DEC-491E-91AC-63513529B551}"/>
+    <hyperlink ref="I11" r:id="rId43" display="Wireframes\0090ExploreMaps.png" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I26" r:id="rId44" display="Wireframes\0052OwnerE-BikeListing-Form.png" xr:uid="{1A0FD9A8-A02A-4E85-8EEB-D06A3AF3294C}"/>
+    <hyperlink ref="I27" r:id="rId45" display="Wireframes\0052OwnerE-BikeListing-Form.png" xr:uid="{044FC5ED-39AA-4080-A3DC-B439F93927B5}"/>
+    <hyperlink ref="I44" r:id="rId46" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{93ACDCC0-A02A-4C0F-B3CD-8D43029AFB07}"/>
+    <hyperlink ref="H44" r:id="rId47" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{E2F540E0-19F6-4F94-A0A2-3BC06D68C587}"/>
+    <hyperlink ref="H46" r:id="rId48" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{692C4001-F76C-4868-ADBB-B6860829A5DB}"/>
+    <hyperlink ref="I47" r:id="rId49" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{927E8FB1-B6B7-4953-9C69-3804D1E25F6E}"/>
+    <hyperlink ref="H47" r:id="rId50" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{4FFB3AB2-680C-4078-8555-E258845D732F}"/>
+    <hyperlink ref="I48" r:id="rId51" display="Wireframes\0075RenterE-BikeBooking-SelectedBike'sOwnerDetails.png" xr:uid="{9A2FCA9B-F158-47F1-8E82-1C4F3E573697}"/>
+    <hyperlink ref="H48" r:id="rId52" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{BC83D10E-8EDE-451A-8B92-5C76042094C4}"/>
+    <hyperlink ref="H51" r:id="rId53" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{C89065FA-D199-44A4-8F21-6A5784EF30B0}"/>
+    <hyperlink ref="I51" r:id="rId54" display="Wireframes\0074RenterE-BikeBookingInsuranceDetails.png" xr:uid="{236BB8F4-9009-4592-A58E-E1E6F103B0E6}"/>
+    <hyperlink ref="H53" r:id="rId55" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{5B52867C-3CB9-4EF9-BE50-53D66F9CEDB3}"/>
+    <hyperlink ref="I53" r:id="rId56" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{86A1D131-334C-4475-BFB6-4967A44E9E8D}"/>
+    <hyperlink ref="H56" r:id="rId57" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{0E60B01E-6207-4C2C-9B2A-8E69BBEA77C4}"/>
+    <hyperlink ref="H57" r:id="rId58" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
+    <hyperlink ref="H58" r:id="rId59" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
+    <hyperlink ref="H59" r:id="rId60" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
+    <hyperlink ref="H60" r:id="rId61" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
+    <hyperlink ref="I60" r:id="rId62" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
+    <hyperlink ref="H61" r:id="rId63" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
+    <hyperlink ref="H62" r:id="rId64" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
+    <hyperlink ref="H63" r:id="rId65" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
+    <hyperlink ref="H64" r:id="rId66" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
+    <hyperlink ref="H65" r:id="rId67" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
+    <hyperlink ref="H66" r:id="rId68" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId46"/>
+  <pageSetup orientation="portrait" r:id="rId69"/>
 </worksheet>
 </file>
--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA4466E-FB67-40C2-85F3-2FE2260D9A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B52A9B-5472-4A86-83E6-0E29922BEA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="19200" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -776,9 +776,6 @@
     <t>0090ExploreMaps.png</t>
   </si>
   <si>
-    <t>1.8</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">press the </t>
     </r>
@@ -4682,6 +4679,9 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>1.12</t>
   </si>
 </sst>
 </file>
@@ -4882,9 +4882,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -4905,6 +4902,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5211,31 +5211,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -5245,8 +5245,8 @@
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -5259,13 +5259,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>30</v>
@@ -5281,7 +5281,7 @@
         <v>1.2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>27</v>
@@ -5337,7 +5337,7 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>40</v>
@@ -5357,7 +5357,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>40</v>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5492,19 +5492,19 @@
         <v>1.8</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>40</v>
@@ -5518,10 +5518,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5532,7 +5532,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>47</v>
@@ -5541,43 +5541,45 @@
     <row r="16" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="7"/>
+      <c r="C16" s="7">
+        <v>1.9</v>
+      </c>
       <c r="D16" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="10" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -5603,7 +5605,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -5617,7 +5619,7 @@
         <v>13</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -5628,10 +5630,10 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -5642,42 +5644,42 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="1"/>
       <c r="C23" s="7">
-        <v>1.9</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="1"/>
       <c r="C24" s="10" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>21</v>
@@ -5686,7 +5688,7 @@
         <v>16</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>44</v>
@@ -5697,7 +5699,7 @@
       <c r="B25" s="1"/>
       <c r="C25" s="7"/>
       <c r="D25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>21</v>
@@ -5706,7 +5708,7 @@
         <v>16</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>45</v>
@@ -5717,28 +5719,28 @@
         <v>2</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C26" s="8">
         <v>2.1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>45</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.3">
@@ -5746,22 +5748,22 @@
       <c r="B27" s="4"/>
       <c r="C27" s="8"/>
       <c r="D27" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>130</v>
-      </c>
       <c r="G27" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
@@ -5771,16 +5773,16 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F28" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>71</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>46</v>
@@ -5793,19 +5795,19 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G29" s="4" t="s">
+      <c r="H29" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -5816,7 +5818,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H30" s="4"/>
     </row>
@@ -5827,19 +5829,19 @@
         <v>2.4</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="G31" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -5849,16 +5851,16 @@
         <v>2.5</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="G32" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H32" s="4"/>
     </row>
@@ -5870,7 +5872,7 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H33" s="4"/>
     </row>
@@ -5881,16 +5883,16 @@
         <v>2.6</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="H34" s="4"/>
     </row>
@@ -5902,10 +5904,10 @@
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
       <c r="G35" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H35" s="18" t="s">
         <v>97</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -5916,7 +5918,7 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H36" s="4"/>
     </row>
@@ -5927,19 +5929,19 @@
         <v>2.7</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="H37" s="12" t="s">
         <v>85</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -5950,7 +5952,7 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H38" s="4"/>
     </row>
@@ -5962,7 +5964,7 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H39" s="4"/>
     </row>
@@ -5974,10 +5976,10 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6011,16 +6013,16 @@
         <v>2.8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F43" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>46</v>
@@ -6040,19 +6042,19 @@
         <v>3</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H44" s="14" t="s">
         <v>44</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -6063,7 +6065,7 @@
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H45" s="5"/>
     </row>
@@ -6075,10 +6077,10 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -6091,19 +6093,19 @@
         <v>3</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="G47" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>44</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -6116,19 +6118,19 @@
         <v>3</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="G48" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="I48" s="14" t="s">
         <v>139</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6139,7 +6141,7 @@
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H49" s="5"/>
     </row>
@@ -6151,7 +6153,7 @@
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H50" s="5"/>
     </row>
@@ -6165,19 +6167,19 @@
         <v>3</v>
       </c>
       <c r="E51" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="G51" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="H51" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -6188,7 +6190,7 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H52" s="5"/>
     </row>
@@ -6202,19 +6204,19 @@
         <v>3</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>150</v>
-      </c>
       <c r="H53" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6224,19 +6226,19 @@
         <v>3.6</v>
       </c>
       <c r="D54" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="F54" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="G54" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -6247,10 +6249,10 @@
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -6258,247 +6260,247 @@
       <c r="B56" s="5"/>
       <c r="C56" s="13"/>
       <c r="D56" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="F56" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="G56" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="H56" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A57" s="20">
+      <c r="A57" s="19">
         <v>4</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" s="19">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D57" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C57" s="20">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D57" s="21" t="s">
+      <c r="E57" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="E57" s="21" t="s">
+      <c r="F57" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="F57" s="21" t="s">
+      <c r="G57" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="H57" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="19"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H58" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="G57" s="21" t="s">
+    </row>
+    <row r="59" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="19"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="H59" s="21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="19"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="H60" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="I60" s="21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="19"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F61" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="H57" s="22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="20"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="H58" s="22" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="20"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="H59" s="22" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="20"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="I60" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="20"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="20">
-        <v>4.2</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="F61" s="21" t="s">
+      <c r="G61" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="G61" s="21" t="s">
+      <c r="H61" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="H61" s="22" t="s">
+    </row>
+    <row r="62" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="19"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19">
+        <v>4.3</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E62" s="20" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="20"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20">
-        <v>4.3</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="E62" s="21" t="s">
+      <c r="F62" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="G62" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="H62" s="22" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="19"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E63" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="F62" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="G62" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="H62" s="23" t="s">
+      <c r="F63" s="20" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="20"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="F63" s="21" t="s">
+      <c r="G63" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="G63" s="21" t="s">
+      <c r="H63" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="H63" s="23" t="s">
+    </row>
+    <row r="64" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="23">
+        <v>5</v>
+      </c>
+      <c r="B64" s="24" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="24">
-        <v>5</v>
-      </c>
-      <c r="B64" s="25" t="s">
+      <c r="C64" s="23">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E64" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="24">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="E64" s="25" t="s">
+      <c r="F64" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="F64" s="25" t="s">
+      <c r="G64" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="G64" s="25" t="s">
+      <c r="H64" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="H64" s="26" t="s">
+    </row>
+    <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="23"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="23">
+        <v>5.2</v>
+      </c>
+      <c r="D65" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" s="24" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="24"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="24">
-        <v>5.2</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="E65" s="25" t="s">
+      <c r="F65" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="F65" s="25" t="s">
+      <c r="G65" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="G65" s="25" t="s">
+      <c r="H65" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="H65" s="26" t="s">
+    </row>
+    <row r="66" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="23"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="23">
+        <v>5.3</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E66" s="24" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="24"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="24">
-        <v>5.3</v>
-      </c>
-      <c r="D66" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="E66" s="25" t="s">
+      <c r="F66" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="F66" s="25" t="s">
+      <c r="G66" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G66" s="25" t="s">
+      <c r="H66" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="H66" s="26" t="s">
+    </row>
+    <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="23"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="23">
+        <v>5.4</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="24"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="24">
-        <v>5.4</v>
-      </c>
-      <c r="D67" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="E67" s="25" t="s">
+      <c r="F67" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="F67" s="25" t="s">
+      <c r="G67" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="G67" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="H67" s="25"/>
+      <c r="H67" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B52A9B-5472-4A86-83E6-0E29922BEA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D059B1D5-31EB-4B34-B24B-E287F7CE150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4789,7 +4789,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4812,21 +4812,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4868,9 +4859,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5211,31 +5199,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -5245,8 +5233,8 @@
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -5345,7 +5333,7 @@
       <c r="I6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5767,24 +5755,24 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="16">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="15">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G28" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="18" t="s">
+      <c r="H28" s="17" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5897,16 +5885,16 @@
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="16"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17" t="s">
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="17" t="s">
         <v>97</v>
       </c>
     </row>
@@ -6276,231 +6264,231 @@
       </c>
     </row>
     <row r="57" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A57" s="19">
+      <c r="A57" s="18">
         <v>4</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="C57" s="19">
+      <c r="C57" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D57" s="20" t="s">
+      <c r="D57" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="F57" s="20" t="s">
+      <c r="F57" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="G57" s="20" t="s">
+      <c r="G57" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="H57" s="21" t="s">
+      <c r="H57" s="20" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="19"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20" t="s">
+      <c r="A58" s="18"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="H58" s="21" t="s">
+      <c r="H58" s="20" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="19"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20" t="s">
+      <c r="A59" s="18"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="H59" s="21" t="s">
+      <c r="H59" s="20" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="19"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20" t="s">
+      <c r="A60" s="18"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="H60" s="21" t="s">
+      <c r="H60" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="I60" s="21" t="s">
+      <c r="I60" s="20" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="19">
+      <c r="A61" s="18"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="18">
         <v>4.2</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D61" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="E61" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F61" s="20" t="s">
+      <c r="F61" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="20" t="s">
+      <c r="G61" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="H61" s="21" t="s">
+      <c r="H61" s="20" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18">
         <v>4.3</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="F62" s="20" t="s">
+      <c r="F62" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="G62" s="20" t="s">
+      <c r="G62" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="H62" s="22" t="s">
+      <c r="H62" s="21" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="F63" s="20" t="s">
+      <c r="F63" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G63" s="20" t="s">
+      <c r="G63" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="21" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="23">
+      <c r="A64" s="22">
         <v>5</v>
       </c>
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="C64" s="23">
+      <c r="C64" s="22">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D64" s="24" t="s">
+      <c r="D64" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="E64" s="24" t="s">
+      <c r="E64" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="F64" s="24" t="s">
+      <c r="F64" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="G64" s="24" t="s">
+      <c r="G64" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="H64" s="25" t="s">
+      <c r="H64" s="24" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="23"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="23">
+      <c r="A65" s="22"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="22">
         <v>5.2</v>
       </c>
-      <c r="D65" s="24" t="s">
+      <c r="D65" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="F65" s="24" t="s">
+      <c r="F65" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="G65" s="24" t="s">
+      <c r="G65" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="H65" s="25" t="s">
+      <c r="H65" s="24" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="23"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="23">
+      <c r="A66" s="22"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="22">
         <v>5.3</v>
       </c>
-      <c r="D66" s="24" t="s">
+      <c r="D66" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="24" t="s">
+      <c r="F66" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="G66" s="24" t="s">
+      <c r="G66" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="H66" s="25" t="s">
+      <c r="H66" s="24" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="23"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="23">
+      <c r="A67" s="22"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="22">
         <v>5.4</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="D67" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="F67" s="24" t="s">
+      <c r="F67" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="G67" s="24" t="s">
+      <c r="G67" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="H67" s="24"/>
+      <c r="H67" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D059B1D5-31EB-4B34-B24B-E287F7CE150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4DF5F2-37FA-44A5-8F3A-E444889FF24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4DF5F2-37FA-44A5-8F3A-E444889FF24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA07CC1-8187-4985-A832-16008A5AD899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="200">
   <si>
     <t>As a</t>
   </si>
@@ -434,9 +434,6 @@
     </r>
   </si>
   <si>
-    <t>1.10</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">I can explore the Micro2Move app's </t>
     </r>
@@ -4692,7 +4689,7 @@
     </r>
   </si>
   <si>
-    <t>1.12</t>
+    <t>1.6</t>
   </si>
 </sst>
 </file>
@@ -5258,13 +5255,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>30</v>
@@ -5280,7 +5277,7 @@
         <v>1.2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>27</v>
@@ -5311,41 +5308,39 @@
         <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="7">
-        <v>1.4</v>
-      </c>
+      <c r="C6" s="7"/>
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="161.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5356,19 +5351,19 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5379,20 +5374,20 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="1"/>
       <c r="C9" s="7">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>32</v>
@@ -5404,21 +5399,19 @@
         <v>35</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="7">
-        <v>1.6</v>
-      </c>
+      <c r="C10" s="7"/>
       <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
@@ -5429,41 +5422,39 @@
         <v>36</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="7">
-        <v>1.7</v>
-      </c>
+      <c r="C11" s="7"/>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -5471,42 +5462,42 @@
       <c r="B12" s="1"/>
       <c r="C12" s="7"/>
       <c r="D12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="1"/>
       <c r="C13" s="7">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="I13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -5517,10 +5508,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5531,54 +5522,52 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="7">
-        <v>1.9</v>
-      </c>
+      <c r="C16" s="7"/>
       <c r="D16" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="10" t="s">
-        <v>38</v>
+        <v>199</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -5604,7 +5593,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -5618,7 +5607,7 @@
         <v>13</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -5629,10 +5618,10 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -5643,42 +5632,38 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="7">
-        <v>1.1100000000000001</v>
-      </c>
+      <c r="C23" s="7"/>
       <c r="D23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="10" t="s">
-        <v>200</v>
-      </c>
+      <c r="C24" s="10"/>
       <c r="D24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>21</v>
@@ -5687,10 +5672,10 @@
         <v>16</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
@@ -5698,7 +5683,7 @@
       <c r="B25" s="1"/>
       <c r="C25" s="7"/>
       <c r="D25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>21</v>
@@ -5707,10 +5692,10 @@
         <v>16</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5718,28 +5703,28 @@
         <v>2</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" s="8">
         <v>2.1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.3">
@@ -5747,22 +5732,22 @@
       <c r="B27" s="4"/>
       <c r="C27" s="8"/>
       <c r="D27" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="G27" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
@@ -5772,19 +5757,19 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F28" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="16" t="s">
-        <v>70</v>
-      </c>
       <c r="H28" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
@@ -5794,19 +5779,19 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="4" t="s">
+      <c r="H29" s="12" t="s">
         <v>67</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -5817,7 +5802,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H30" s="4"/>
     </row>
@@ -5828,19 +5813,19 @@
         <v>2.4</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="G31" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -5850,16 +5835,16 @@
         <v>2.5</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="G32" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H32" s="4"/>
     </row>
@@ -5871,7 +5856,7 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H33" s="4"/>
     </row>
@@ -5882,16 +5867,16 @@
         <v>2.6</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="H34" s="4"/>
     </row>
@@ -5903,10 +5888,10 @@
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
       <c r="G35" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" s="17" t="s">
         <v>96</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -5917,7 +5902,7 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H36" s="4"/>
     </row>
@@ -5928,19 +5913,19 @@
         <v>2.7</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="H37" s="12" t="s">
         <v>84</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -5951,7 +5936,7 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H38" s="4"/>
     </row>
@@ -5963,7 +5948,7 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H39" s="4"/>
     </row>
@@ -5975,10 +5960,10 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6012,19 +5997,19 @@
         <v>2.8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F43" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="H43" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6041,19 +6026,19 @@
         <v>3</v>
       </c>
       <c r="E44" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I44" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -6064,7 +6049,7 @@
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H45" s="5"/>
     </row>
@@ -6076,10 +6061,10 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -6092,19 +6077,19 @@
         <v>3</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="G47" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I47" s="14" t="s">
         <v>103</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -6117,19 +6102,19 @@
         <v>3</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="G48" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="I48" s="14" t="s">
         <v>138</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6140,7 +6125,7 @@
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H49" s="5"/>
     </row>
@@ -6152,7 +6137,7 @@
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H50" s="5"/>
     </row>
@@ -6166,19 +6151,19 @@
         <v>3</v>
       </c>
       <c r="E51" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="G51" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="H51" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -6189,7 +6174,7 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H52" s="5"/>
     </row>
@@ -6203,19 +6188,19 @@
         <v>3</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="H53" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6225,19 +6210,19 @@
         <v>3.6</v>
       </c>
       <c r="D54" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="F54" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="G54" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -6248,10 +6233,10 @@
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -6259,19 +6244,19 @@
       <c r="B56" s="5"/>
       <c r="C56" s="13"/>
       <c r="D56" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="F56" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="G56" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="H56" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -6279,25 +6264,25 @@
         <v>4</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57" s="18">
         <v>4.0999999999999996</v>
       </c>
       <c r="D57" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="F57" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="F57" s="19" t="s">
-        <v>163</v>
-      </c>
       <c r="G57" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -6308,10 +6293,10 @@
       <c r="E58" s="19"/>
       <c r="F58" s="19"/>
       <c r="G58" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6322,10 +6307,10 @@
       <c r="E59" s="19"/>
       <c r="F59" s="19"/>
       <c r="G59" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -6336,13 +6321,13 @@
       <c r="E60" s="19"/>
       <c r="F60" s="19"/>
       <c r="G60" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="H60" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="H60" s="20" t="s">
+      <c r="I60" s="20" t="s">
         <v>169</v>
-      </c>
-      <c r="I60" s="20" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6352,19 +6337,19 @@
         <v>4.2</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F61" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G61" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="19" t="s">
+      <c r="H61" s="20" t="s">
         <v>174</v>
-      </c>
-      <c r="H61" s="20" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6374,19 +6359,19 @@
         <v>4.3</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F62" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="G62" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="H62" s="21" t="s">
         <v>179</v>
-      </c>
-      <c r="H62" s="21" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6396,19 +6381,19 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F63" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="G63" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G63" s="19" t="s">
+      <c r="H63" s="21" t="s">
         <v>182</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -6416,25 +6401,25 @@
         <v>5</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C64" s="22">
         <v>5.0999999999999996</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E64" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F64" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="F64" s="23" t="s">
+      <c r="G64" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="H64" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="H64" s="24" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6444,19 +6429,19 @@
         <v>5.2</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E65" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="F65" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="F65" s="23" t="s">
+      <c r="G65" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="G65" s="23" t="s">
+      <c r="H65" s="24" t="s">
         <v>191</v>
-      </c>
-      <c r="H65" s="24" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6466,19 +6451,19 @@
         <v>5.3</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E66" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="F66" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="23" t="s">
+      <c r="G66" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="G66" s="23" t="s">
+      <c r="H66" s="24" t="s">
         <v>195</v>
-      </c>
-      <c r="H66" s="24" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6488,16 +6473,16 @@
         <v>5.4</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E67" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="F67" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="F67" s="23" t="s">
+      <c r="G67" s="23" t="s">
         <v>198</v>
-      </c>
-      <c r="G67" s="23" t="s">
-        <v>199</v>
       </c>
       <c r="H67" s="23"/>
     </row>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA07CC1-8187-4985-A832-16008A5AD899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA972DC-15FB-4601-BB6F-FDC4619E0148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="13212" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="196">
   <si>
     <t>As a</t>
   </si>
@@ -1090,9 +1090,6 @@
     <t>owner</t>
   </si>
   <si>
-    <t>I must be able to upload an image of my e-bike</t>
-  </si>
-  <si>
     <t>0052OwnerE-BikeListing-Form.png</t>
   </si>
   <si>
@@ -1280,9 +1277,6 @@
     </r>
   </si>
   <si>
-    <t>I must be able to put in a unique name to my e-bike, set a start date and end date for the listing, set a price per week in Au$, Select an e-bike category and set a pickup and drop-off address.</t>
-  </si>
-  <si>
     <t>0053OwnerE-BikeHealthChecklist.png</t>
   </si>
   <si>
@@ -1843,7 +1837,338 @@
     <t>0072RenterE-BikeBooking-BikeDetails.png</t>
   </si>
   <si>
-    <t>If no Matching e-bikes are found, I must see a proper message.</t>
+    <t>I can view the details of the same bike.</t>
+  </si>
+  <si>
+    <t>0073RenterE-BikeBookingConfirmation.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can view the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Listing Form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav tab </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Your First E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Listing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If my credentials are valid and I have started from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rent a Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Landing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Screen, I must be logged in into my account in Micro2Move app and subsequently landing on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Renter E-BikeBooking Filter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen (with a personalized welcome note on top) on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">My Rides </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bottom navigation tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If my credentials are valid and I have started from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List a Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Landing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Screen, I must be logged in into my account in Micro2Move app and subsequently landing on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Owner E-Bike Listing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(In case I have no bikes listed)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">/ Owner Existing E-Bikes List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(In case I have one or more bikes listed) screen (with a personalized welcome note on top) on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottom navigation tab</t>
+    </r>
+  </si>
+  <si>
+    <t>un-logged-in user</t>
   </si>
   <si>
     <r>
@@ -1858,6 +2183,2241 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Or the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav Tabs, while I am on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav Tab</t>
+    </r>
+  </si>
+  <si>
+    <t>ExploreBottomNavTab.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be landing on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sign In </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen.</t>
+    </r>
+  </si>
+  <si>
+    <t>On Successful submission of valid credential, I must land on the respective Bottom Nav Tab</t>
+  </si>
+  <si>
+    <t>I can list or rent bike(s) or use other features of the Micro2Move app</t>
+  </si>
+  <si>
+    <t>owner/ renter/ logged-in user/ un-logged-in user</t>
+  </si>
+  <si>
+    <t>logged-in user</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can visit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Or the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tabs</t>
+    </r>
+  </si>
+  <si>
+    <t>I must be landing on the respective tab</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> My Bikes, Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Or the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav Tabs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can visit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes, Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Or the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tabs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If I press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Continue </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button and my registration details are invalid I must see respective error messages on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>User</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Registration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen itself</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to visit details </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Terms and Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> link, scroll up to see all the details and navigate back by clicking </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button</t>
+    </r>
+  </si>
+  <si>
+    <t>unregistered renter</t>
+  </si>
+  <si>
+    <t>unregistered owner</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On submission of invalid credential, I must see respective error messages on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SignIn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">owner with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>existing listed bikes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">owner with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no listed bikes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Another E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerExistingE-BikesList.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can view the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerE-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Listing-Form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav tab </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to view a welcome message with my name, the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Your First E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> big button and a list of benefits of listing my bike in this screen on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to view a welcome message with my name, my previously listed bikes and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>List Another E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button in this screen on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Nav tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to visit details of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Owner E-Bike Health Checklist </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">link and navigate back by clicking </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If all mandatory and legit details are not provided in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Owner E-Bike Listing Form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, the same form/ screen must reappear back with respective error messages.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to view the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen with the details of the e-bike selected by me.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see a list of matching e-bikes in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBooking-BikeDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sorted in ascending order of price.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view the details of the same bike's owner</t>
+  </si>
+  <si>
+    <t>0075RenterE-BikeBooking-SelectedBike'sOwnerDetails.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be navigated back to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeBookingConfirmation </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen if I click on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Learn More </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view the detailed insurance policy</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see the full insurance policy and an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see the owner's name, short bio, number of the e-bikes listed by them so far, rating with the number of raters, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Community Activities</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink and an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button.</t>
+    </r>
+  </si>
+  <si>
+    <t>0074RenterE-BikeBookingInsuranceDetails.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Book </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can book my desired e-bike</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If I have checked the checkbox for purchase mandatory insurance and pressed the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button, my bike must be booked and I must be navigated to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterBookedBikesList </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen, where the recently booked e-bike should be shown at the TOP.</t>
+    </r>
+  </si>
+  <si>
+    <t>I can start booking my desired e-bike</t>
+  </si>
+  <si>
+    <t>Wireframe TBD</t>
+  </si>
+  <si>
+    <t>Explore</t>
+  </si>
+  <si>
+    <t>Logged in user</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Explore </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bottom nav tab</t>
+    </r>
+  </si>
+  <si>
+    <t>I can browse the explore features on micro2move app</t>
+  </si>
+  <si>
+    <t>0091ExploreMapsNavigation.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to enter address of my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Starting Point</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Destination</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> upon tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bar on map.</t>
+    </r>
+  </si>
+  <si>
+    <t>0092ExploreMapsNavigationFlow.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see the best possible route to my destination on the map upon successfully entering my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Starting Point</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Destination</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, according to real-time updates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see toggles for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Current Charging Stations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Future Charging Stations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dedicated Bike Stations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bike Lane Infrastructure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when I click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">More </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>icon on the map and should reflect the respective information on map upon toggling them on.</t>
+    </r>
+  </si>
+  <si>
+    <t>0093ExploreMapsMoreOptions.png</t>
+  </si>
+  <si>
+    <t>0094ExploreMapsBikeLanes.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Info </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see a map of my locality, a location search bar, an option to see </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>More</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e-bike related information on map, an option for zooming in and out of the map and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Info</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Community Update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ask AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlinks.</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view more information on what concerns me about micro2move</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see relevant information about micro2move on the info screen, with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Info </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
+    </r>
+  </si>
+  <si>
+    <t>0100ExploreInfo.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Community Update </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ask AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <t>I can see all the commnity updates</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see community updates (if any) screen, with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Community Updates </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
+    </r>
+  </si>
+  <si>
+    <t>0110ExploreCommunityUpdates.png</t>
+  </si>
+  <si>
+    <t>I can chat with AI about traffic, e-bike routes etc.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see a text field where I can type my prompt and an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ask AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button, with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ask AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
+    </r>
+  </si>
+  <si>
+    <t>0120ExploreAskAI.png</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bottom nav tab</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view and edit my profile's private and public details</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to see and edit my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile Picture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, view-only Name,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Email, Number and renter rating of my</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Listed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e-bikes, Number and Owner Rating</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">of my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rented</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e-bikes, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Joining Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Community Activity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In-App Lessons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Logout </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>options.</t>
+    </r>
+  </si>
+  <si>
+    <t>0130Profile.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Community Activity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">option in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view ongoing activities and sign myself up for them.</t>
+  </si>
+  <si>
+    <t>I must be able to view details and sign myself up for the activities listed on the screen.</t>
+  </si>
+  <si>
+    <t>0131ProfileCommunityActivity.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">In-App Lessons </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">option in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view interactive lessons regarding e-bikes, traffic and safety measures.</t>
+  </si>
+  <si>
+    <t>I must be able to view and interact with the lessons listed on the screen.</t>
+  </si>
+  <si>
+    <t>0132ProfileLessons.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Logout </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">option in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can logout from the micro2move app.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be logged out from the app and be redirected to the landing screen upon pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Logout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>I must be able to click a photo of my e-bike</t>
+  </si>
+  <si>
+    <t>I must be able to put in a unique name to my e-bike, set a start date and end date (end time &gt; start time) for the listing, set a price per week in Au$, Select an e-bike category and set a pickup and drop-off address.</t>
+  </si>
+  <si>
+    <t>Renters must also be able to see the updated info in their respective bikes' listing screens</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Continue </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button style must be primary and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Visit My Bookings </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>secondary</t>
+    </r>
+  </si>
+  <si>
+    <t>If no Matching e-bikes are found, I must see a proper message. (No E-Bikes are found. Consider increasing your budget.)</t>
+  </si>
+  <si>
+    <t>If one or more bikes are found matching my filters, the cheapest bike must be showed on top with larger image and details. The rest of the bikes must be showed as a list, in ascending order of price (cheapest &gt; costliest)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Book This Bike</t>
     </r>
     <r>
@@ -1910,81 +4470,44 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> any of the bikes listed in the same screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view the details of the same bike.</t>
-  </si>
-  <si>
-    <t>0073RenterE-BikeBookingConfirmation.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can view the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Listing Form</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav tab </t>
+      <t xml:space="preserve"> any of the bikes (cards) listed in the same screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be navigated to view the owner's community activties if I click on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Community Activities </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
     </r>
   </si>
   <si>
@@ -2000,7 +4523,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>List Your First E-Bike</t>
+      <t>Book an E-Bike</t>
     </r>
     <r>
       <rPr>
@@ -2021,7 +4544,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Owner E-Bike Listing</t>
+      <t xml:space="preserve">RenterBookedBikesList </t>
     </r>
     <r>
       <rPr>
@@ -2033,223 +4556,52 @@
       </rPr>
       <t xml:space="preserve"> screen</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If my credentials are valid and I have started from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rent a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Landing </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Screen, I must be logged in into my account in Micro2Move app and subsequently landing on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Renter E-BikeBooking Filter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen (with a personalized welcome note on top) on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">My Rides </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bottom navigation tab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If my credentials are valid and I have started from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Landing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Screen, I must be logged in into my account in Micro2Move app and subsequently landing on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Owner E-Bike Listing </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(In case I have no bikes listed)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">/ Owner Existing E-Bikes List </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">(In case I have one or more bikes listed) screen (with a personalized welcome note on top) on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottom navigation tab</t>
-    </r>
-  </si>
-  <si>
-    <t>un-logged-in user</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be navigated to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeBookingFilter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen with a welcome message with my name and a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book an E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> caption on the </t>
     </r>
     <r>
       <rPr>
@@ -2270,2426 +4622,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Or the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav Tabs, while I am on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav Tab</t>
-    </r>
-  </si>
-  <si>
-    <t>ExploreBottomNavTab.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be landing on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Sign In </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen.</t>
-    </r>
-  </si>
-  <si>
-    <t>On Successful submission of valid credential, I must land on the respective Bottom Nav Tab</t>
-  </si>
-  <si>
-    <t>I can list or rent bike(s) or use other features of the Micro2Move app</t>
-  </si>
-  <si>
-    <t>owner/ renter/ logged-in user/ un-logged-in user</t>
-  </si>
-  <si>
-    <t>logged-in user</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can visit </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Or the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tabs</t>
-    </r>
-  </si>
-  <si>
-    <t>I must be landing on the respective tab</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> My Bikes, Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Or the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav Tabs</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can visit </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes, Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Or the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tabs</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If I press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Continue </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">button and my registration details are invalid I must see respective error messages on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>User</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Registration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen itself</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to visit details </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Terms and Conditions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> link, scroll up to see all the details and navigate back by clicking </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button</t>
-    </r>
-  </si>
-  <si>
-    <t>unregistered renter</t>
-  </si>
-  <si>
-    <t>unregistered owner</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">On submission of invalid credential, I must see respective error messages on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SignIn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">owner with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>existing listed bikes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">owner with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>no listed bikes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List Another E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerExistingE-BikesList.png</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can view the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerE-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Listing-Form</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav tab </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to view a welcome message with my name, the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List Your First E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> big button and a list of benefits of listing my bike in this screen on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav tab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to view a welcome message with my name, my previously listed bikes and the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List Another E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button in this screen on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Nav tab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to visit details of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Owner E-Bike Health Checklist </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">link and navigate back by clicking </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If all mandatory and legit details are not provided in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Owner E-Bike Listing Form</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, the same form/ screen must reappear back with respective error messages.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to view the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingConfirmation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen with the details of the e-bike selected by me.</t>
-    </r>
-  </si>
-  <si>
-    <t>If one or more bikes are found matching my filters, the first bike must be showed on top with larger image and details. The rest of the bikes must be showed as a list.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see a list of matching e-bikes in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBooking-BikeDetails</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sorted in ascending order of price.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Owner's Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingConfirmation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view the details of the same bike's owner</t>
-  </si>
-  <si>
-    <t>0075RenterE-BikeBooking-SelectedBike'sOwnerDetails.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must to navigated to view the owner's community activties if I click on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Community Activities </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hyperlink.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be navigated back to the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">RenterE-BikeBookingConfirmation </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">screen if I click on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">OK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>button.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Learn More </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Insurance</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingConfirmation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view the detailed insurance policy</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see the full insurance policy and an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see the owner's name, short bio, number of the e-bikes listed by them so far, rating with the number of raters, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Community Activities</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink and an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button.</t>
-    </r>
-  </si>
-  <si>
-    <t>0074RenterE-BikeBookingInsuranceDetails.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Book </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingConfirmation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can book my desired e-bike</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If I have checked the checkbox for purchase mandatory insurance and pressed the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button, my bike must be booked and I must be navigated to the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">RenterBookedBikesList </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen, where the recently booked e-bike should be shown at the TOP.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">renter with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>no booked e-bikes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book Your First E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button</t>
-    </r>
-  </si>
-  <si>
-    <t>I can start booking my desired e-bike</t>
-  </si>
-  <si>
-    <t>Wireframe TBD</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be navigated to the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">RenterE-BikeBookingFilter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">screen upon pressing the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book Your First E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">renter with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>existing booked e-bikes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book an E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button</t>
-    </r>
-  </si>
-  <si>
-    <t>I can start booking another e-bike</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see a welcome message with my name, a date filter to sort my e-bikes based on booking time, my previously booked bikes with their respective details and a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Book an E-Bike </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">My Rides </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see a welcome message with my name, benefits of booking an e-bike with micro2move and a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Book Your First E-Bike </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">button on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> tab.</t>
     </r>
-  </si>
-  <si>
-    <t>Explore</t>
-  </si>
-  <si>
-    <t>Logged in user</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Explore </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bottom nav tab</t>
-    </r>
-  </si>
-  <si>
-    <t>I can browse the explore features on micro2move app</t>
-  </si>
-  <si>
-    <t>0091ExploreMapsNavigation.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to enter address of my </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Starting Point</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Destination</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> upon tapping the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>search</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bar on map.</t>
-    </r>
-  </si>
-  <si>
-    <t>0092ExploreMapsNavigationFlow.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see the best possible route to my destination on the map upon successfully entering my </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Starting Point</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Destination</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, according to real-time updates.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see toggles for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Current Charging Stations</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Future Charging Stations</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dedicated Bike Stations</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bike Lane Infrastructure</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> when I click on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">More </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>icon on the map and should reflect the respective information on map upon toggling them on.</t>
-    </r>
-  </si>
-  <si>
-    <t>0093ExploreMapsMoreOptions.png</t>
-  </si>
-  <si>
-    <t>0094ExploreMapsBikeLanes.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Info </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hyperlink</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see a map of my locality, a location search bar, an option to see </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>More</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> e-bike related information on map, an option for zooming in and out of the map and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Info</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Community Update</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ask AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlinks.</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view more information on what concerns me about micro2move</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see relevant information about micro2move on the info screen, with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Info </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
-    </r>
-  </si>
-  <si>
-    <t>0100ExploreInfo.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Community Update </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hyperlink</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Ask AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hyperlink</t>
-    </r>
-  </si>
-  <si>
-    <t>I can see all the commnity updates</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see community updates (if any) screen, with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Community Updates </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
-    </r>
-  </si>
-  <si>
-    <t>0110ExploreCommunityUpdates.png</t>
-  </si>
-  <si>
-    <t>I can chat with AI about traffic, e-bike routes etc.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see a text field where I can type my prompt and an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ask AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button, with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Ask AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hyperlink highlighted and the rest present as navigable hyperlinks</t>
-    </r>
-  </si>
-  <si>
-    <t>0120ExploreAskAI.png</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Profile </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bottom nav tab</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view and edit my profile's private and public details</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to see and edit my </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile Picture</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, view-only Name,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Email, Number and renter rating of my</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Listed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> e-bikes, Number and Owner Rating</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">of my </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rented</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> e-bikes, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Joining Date </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>and</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Community Activity</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>In-App Lessons</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Logout </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>options.</t>
-    </r>
-  </si>
-  <si>
-    <t>0130Profile.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Community Activity </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">option in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">profile </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view ongoing activities and sign myself up for them.</t>
-  </si>
-  <si>
-    <t>I must be able to view details and sign myself up for the activities listed on the screen.</t>
-  </si>
-  <si>
-    <t>0131ProfileCommunityActivity.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">In-App Lessons </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">option in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">profile </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view interactive lessons regarding e-bikes, traffic and safety measures.</t>
-  </si>
-  <si>
-    <t>I must be able to view and interact with the lessons listed on the screen.</t>
-  </si>
-  <si>
-    <t>0132ProfileLessons.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I want to press on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Logout </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">option in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">profile </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can logout from the micro2move app.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be logged out from the app and be redirected to the landing screen upon pressing </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Logout</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>1.6</t>
   </si>
 </sst>
 </file>
@@ -5255,13 +5189,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>30</v>
@@ -5277,7 +5211,7 @@
         <v>1.2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>27</v>
@@ -5331,7 +5265,7 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>39</v>
@@ -5351,7 +5285,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>39</v>
@@ -5472,7 +5406,7 @@
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5482,19 +5416,19 @@
         <v>1.5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>39</v>
@@ -5508,10 +5442,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5522,7 +5456,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>46</v>
@@ -5533,26 +5467,26 @@
       <c r="B16" s="1"/>
       <c r="C16" s="7"/>
       <c r="D16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="10" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>15</v>
@@ -5632,7 +5566,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>61</v>
@@ -5652,7 +5586,7 @@
         <v>57</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>56</v>
@@ -5663,7 +5597,7 @@
       <c r="B24" s="1"/>
       <c r="C24" s="10"/>
       <c r="D24" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>21</v>
@@ -5683,7 +5617,7 @@
       <c r="B25" s="1"/>
       <c r="C25" s="7"/>
       <c r="D25" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>21</v>
@@ -5709,22 +5643,22 @@
         <v>2.1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>44</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.3">
@@ -5732,22 +5666,22 @@
       <c r="B27" s="4"/>
       <c r="C27" s="8"/>
       <c r="D27" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>45</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
@@ -5760,13 +5694,13 @@
         <v>65</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>69</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>45</v>
@@ -5782,16 +5716,16 @@
         <v>65</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G29" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="H29" s="12" t="s">
         <v>66</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -5802,7 +5736,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="H30" s="4"/>
     </row>
@@ -5816,16 +5750,16 @@
         <v>65</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H31" s="12" t="s">
         <v>73</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -5838,13 +5772,13 @@
         <v>65</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F32" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="H32" s="4"/>
     </row>
@@ -5856,7 +5790,7 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H33" s="4"/>
     </row>
@@ -5870,13 +5804,13 @@
         <v>65</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="H34" s="4"/>
     </row>
@@ -5888,10 +5822,10 @@
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
       <c r="G35" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -5902,7 +5836,7 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H36" s="4"/>
     </row>
@@ -5916,16 +5850,16 @@
         <v>65</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="H37" s="12" t="s">
         <v>82</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -5936,7 +5870,7 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H38" s="4"/>
     </row>
@@ -5948,7 +5882,7 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H39" s="4"/>
     </row>
@@ -5960,10 +5894,10 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6000,60 +5934,60 @@
         <v>65</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="13">
+    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
         <v>3</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="13">
+      <c r="C45" s="13">
         <v>3.1</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F44" s="5" t="s">
+      <c r="E45" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I45" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="5"/>
       <c r="C46" s="13"/>
@@ -6061,110 +5995,97 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>99</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="13">
-        <v>3.3</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>137</v>
-      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="H48" s="14"/>
+    </row>
+    <row r="49" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="C49" s="13">
+        <v>3.2</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="G49" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="50" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="C50" s="13">
+        <v>3.3</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="G50" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="H50" s="5"/>
-    </row>
-    <row r="51" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="13">
-        <v>3.4</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>142</v>
-      </c>
+      <c r="C51" s="13"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I51" s="14" t="s">
-        <v>145</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="H51" s="5"/>
     </row>
     <row r="52" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
@@ -6174,89 +6095,92 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="H52" s="5"/>
     </row>
-    <row r="53" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
       <c r="B53" s="5"/>
       <c r="C53" s="13">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="13">
-        <v>3.6</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>151</v>
-      </c>
+      <c r="C54" s="13"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
       <c r="G54" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="C55" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="G55" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="13"/>
+      <c r="C56" s="13">
+        <v>3.6</v>
+      </c>
       <c r="D56" s="5" t="s">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>96</v>
+        <v>195</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="72" x14ac:dyDescent="0.3">
@@ -6264,22 +6188,22 @@
         <v>4</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C57" s="18">
         <v>4.0999999999999996</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="H57" s="20" t="s">
         <v>51</v>
@@ -6293,10 +6217,10 @@
       <c r="E58" s="19"/>
       <c r="F58" s="19"/>
       <c r="G58" s="19" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6307,10 +6231,10 @@
       <c r="E59" s="19"/>
       <c r="F59" s="19"/>
       <c r="G59" s="19" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -6321,13 +6245,13 @@
       <c r="E60" s="19"/>
       <c r="F60" s="19"/>
       <c r="G60" s="19" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="I60" s="20" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6337,19 +6261,19 @@
         <v>4.2</v>
       </c>
       <c r="D61" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="H61" s="20" t="s">
         <v>160</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="H61" s="20" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6359,19 +6283,19 @@
         <v>4.3</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="H62" s="21" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -6381,19 +6305,19 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="H63" s="21" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -6401,25 +6325,25 @@
         <v>5</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C64" s="22">
         <v>5.0999999999999996</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="G64" s="23" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6429,19 +6353,19 @@
         <v>5.2</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F65" s="23" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="G65" s="23" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6451,19 +6375,19 @@
         <v>5.3</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="F66" s="23" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6473,16 +6397,16 @@
         <v>5.4</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="F67" s="23" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="G67" s="23" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="H67" s="23"/>
     </row>
@@ -6541,31 +6465,30 @@
     <hyperlink ref="I11" r:id="rId43" display="Wireframes\0090ExploreMaps.png" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="I26" r:id="rId44" display="Wireframes\0052OwnerE-BikeListing-Form.png" xr:uid="{1A0FD9A8-A02A-4E85-8EEB-D06A3AF3294C}"/>
     <hyperlink ref="I27" r:id="rId45" display="Wireframes\0052OwnerE-BikeListing-Form.png" xr:uid="{044FC5ED-39AA-4080-A3DC-B439F93927B5}"/>
-    <hyperlink ref="I44" r:id="rId46" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{93ACDCC0-A02A-4C0F-B3CD-8D43029AFB07}"/>
-    <hyperlink ref="H44" r:id="rId47" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{E2F540E0-19F6-4F94-A0A2-3BC06D68C587}"/>
-    <hyperlink ref="H46" r:id="rId48" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{692C4001-F76C-4868-ADBB-B6860829A5DB}"/>
-    <hyperlink ref="I47" r:id="rId49" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{927E8FB1-B6B7-4953-9C69-3804D1E25F6E}"/>
-    <hyperlink ref="H47" r:id="rId50" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{4FFB3AB2-680C-4078-8555-E258845D732F}"/>
-    <hyperlink ref="I48" r:id="rId51" display="Wireframes\0075RenterE-BikeBooking-SelectedBike'sOwnerDetails.png" xr:uid="{9A2FCA9B-F158-47F1-8E82-1C4F3E573697}"/>
-    <hyperlink ref="H48" r:id="rId52" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{BC83D10E-8EDE-451A-8B92-5C76042094C4}"/>
-    <hyperlink ref="H51" r:id="rId53" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{C89065FA-D199-44A4-8F21-6A5784EF30B0}"/>
-    <hyperlink ref="I51" r:id="rId54" display="Wireframes\0074RenterE-BikeBookingInsuranceDetails.png" xr:uid="{236BB8F4-9009-4592-A58E-E1E6F103B0E6}"/>
-    <hyperlink ref="H53" r:id="rId55" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{5B52867C-3CB9-4EF9-BE50-53D66F9CEDB3}"/>
-    <hyperlink ref="I53" r:id="rId56" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{86A1D131-334C-4475-BFB6-4967A44E9E8D}"/>
-    <hyperlink ref="H56" r:id="rId57" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{0E60B01E-6207-4C2C-9B2A-8E69BBEA77C4}"/>
-    <hyperlink ref="H57" r:id="rId58" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
-    <hyperlink ref="H58" r:id="rId59" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
-    <hyperlink ref="H59" r:id="rId60" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
-    <hyperlink ref="H60" r:id="rId61" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
-    <hyperlink ref="I60" r:id="rId62" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
-    <hyperlink ref="H61" r:id="rId63" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
-    <hyperlink ref="H62" r:id="rId64" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
-    <hyperlink ref="H63" r:id="rId65" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
-    <hyperlink ref="H64" r:id="rId66" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
-    <hyperlink ref="H65" r:id="rId67" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
-    <hyperlink ref="H66" r:id="rId68" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
+    <hyperlink ref="I45" r:id="rId46" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{93ACDCC0-A02A-4C0F-B3CD-8D43029AFB07}"/>
+    <hyperlink ref="H45" r:id="rId47" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{E2F540E0-19F6-4F94-A0A2-3BC06D68C587}"/>
+    <hyperlink ref="H47" r:id="rId48" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{692C4001-F76C-4868-ADBB-B6860829A5DB}"/>
+    <hyperlink ref="I49" r:id="rId49" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{927E8FB1-B6B7-4953-9C69-3804D1E25F6E}"/>
+    <hyperlink ref="H49" r:id="rId50" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{4FFB3AB2-680C-4078-8555-E258845D732F}"/>
+    <hyperlink ref="I50" r:id="rId51" display="Wireframes\0075RenterE-BikeBooking-SelectedBike'sOwnerDetails.png" xr:uid="{9A2FCA9B-F158-47F1-8E82-1C4F3E573697}"/>
+    <hyperlink ref="H50" r:id="rId52" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{BC83D10E-8EDE-451A-8B92-5C76042094C4}"/>
+    <hyperlink ref="H53" r:id="rId53" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{C89065FA-D199-44A4-8F21-6A5784EF30B0}"/>
+    <hyperlink ref="I53" r:id="rId54" display="Wireframes\0074RenterE-BikeBookingInsuranceDetails.png" xr:uid="{236BB8F4-9009-4592-A58E-E1E6F103B0E6}"/>
+    <hyperlink ref="H55" r:id="rId55" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{5B52867C-3CB9-4EF9-BE50-53D66F9CEDB3}"/>
+    <hyperlink ref="I55" r:id="rId56" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{86A1D131-334C-4475-BFB6-4967A44E9E8D}"/>
+    <hyperlink ref="H57" r:id="rId57" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
+    <hyperlink ref="H58" r:id="rId58" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
+    <hyperlink ref="H59" r:id="rId59" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
+    <hyperlink ref="H60" r:id="rId60" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
+    <hyperlink ref="I60" r:id="rId61" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
+    <hyperlink ref="H61" r:id="rId62" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
+    <hyperlink ref="H62" r:id="rId63" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
+    <hyperlink ref="H63" r:id="rId64" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
+    <hyperlink ref="H64" r:id="rId65" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
+    <hyperlink ref="H65" r:id="rId66" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
+    <hyperlink ref="H66" r:id="rId67" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId69"/>
+  <pageSetup orientation="portrait" r:id="rId68"/>
 </worksheet>
 </file>
--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA972DC-15FB-4601-BB6F-FDC4619E0148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4879F9F2-4926-40D1-9514-7DF387DB2D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="13212" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -4845,8 +4845,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCECFF"/>
       <color rgb="FFCCFFCC"/>
-      <color rgb="FFCCECFF"/>
       <color rgb="FFFFCCFF"/>
       <color rgb="FF800080"/>
       <color rgb="FFFFFFCC"/>
@@ -5685,24 +5685,24 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="15">
+      <c r="A28" s="8"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="8">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H28" s="17" t="s">
+      <c r="H28" s="12" t="s">
         <v>45</v>
       </c>
     </row>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anodiam\desktop-tutorial\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4879F9F2-4926-40D1-9514-7DF387DB2D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87EB565-289F-4933-8A9C-09B62121BBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="218">
   <si>
     <t>As a</t>
   </si>
@@ -3365,12 +3365,6 @@
     </r>
   </si>
   <si>
-    <t>I can start booking my desired e-bike</t>
-  </si>
-  <si>
-    <t>Wireframe TBD</t>
-  </si>
-  <si>
     <t>Explore</t>
   </si>
   <si>
@@ -4623,6 +4617,481 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <t>renter with existing booked bikes</t>
+  </si>
+  <si>
+    <t>renter with NO existing booked bike</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book Another E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterBookedBikesList </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can start booking another desired e-bike</t>
+  </si>
+  <si>
+    <t>I can start booking my first e-bike</t>
+  </si>
+  <si>
+    <t>0081RenterEmptyBookedBikesList.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on any of the options from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedBikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and check the options  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be navigated to the options for each E-bike listed, such as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ViewOwner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel booking.</t>
+    </r>
+  </si>
+  <si>
+    <t>0082RenterBookedE-BikeOptions.png</t>
+  </si>
+  <si>
+    <t>renter who has clicked on one of the listed options</t>
+  </si>
+  <si>
+    <t>I can view the cancellation policy and options to confirm or not cancel</t>
+  </si>
+  <si>
+    <t>I can view the options for each listing on the E-bike profile page.</t>
+  </si>
+  <si>
+    <t>0083RenterBookedE-BikeCancellationOption.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be navigated to the options on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancellation Policy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> page to find the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price, Cancellation charge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Return amount </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">for the respective E-Bike listed. I should be getting the option to either </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>confirm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the cancellation or to choose </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Do Not Cancel, Go Back</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option. If I click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Confirm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab, I shall be able to proceed with cancellation and if I click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Do Not Cancel, Go Back</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab I should be navigated back to the E-bike's profile page. </t>
+    </r>
+  </si>
+  <si>
+    <t>press on the cancel booking option from the E-bike profile page.</t>
+  </si>
+  <si>
+    <t>renter who has selected his/her desired E-bike</t>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can view all the features of that E-bike and check whether the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toggle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is on for all of them. If any of them is not available, I can raise an issue, otherwise accept the e-bike.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">check the features of the E-bike selected by clicking on the e-bike features link before I choose to click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accept E-bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab or raise an issue. </t>
+    </r>
+  </si>
+  <si>
+    <t>0084RenterBookedE-BikeFeaturesOptions.png</t>
+  </si>
+  <si>
+    <t>0085RenterBookedE-BikeFeaturest2Check.png</t>
+  </si>
+  <si>
+    <t>0086RenterBookedE-BikeRaiseIssue.png</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to check whether all the desired features are available for my selected E-bike. If not, I can raise an issue by clicking on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raise Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.  I should be able to see the screen for raising the issue where I can describe it and upload relevant image for the same. I may also choose to ignore the issue and click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ignore Issue, Go Back </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">option to reach the  E-bike's profile screen with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accept E-bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
   </si>
 </sst>
@@ -4759,7 +5228,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4833,8 +5302,14 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5126,7 +5601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="9" customWidth="1"/>
@@ -5141,31 +5616,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -5175,8 +5650,8 @@
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -5486,7 +5961,7 @@
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>15</v>
@@ -5722,7 +6197,7 @@
         <v>70</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>66</v>
@@ -5736,7 +6211,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H30" s="4"/>
     </row>
@@ -5954,7 +6429,7 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H44" s="12"/>
     </row>
@@ -5995,7 +6470,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H46" s="5"/>
     </row>
@@ -6007,7 +6482,7 @@
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>97</v>
@@ -6021,11 +6496,11 @@
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H48" s="14"/>
     </row>
-    <row r="49" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="5"/>
       <c r="C49" s="13">
@@ -6035,7 +6510,7 @@
         <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>98</v>
@@ -6050,7 +6525,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="5"/>
       <c r="C50" s="13">
@@ -6075,7 +6550,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="5"/>
       <c r="C51" s="13"/>
@@ -6083,11 +6558,11 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H51" s="5"/>
     </row>
-    <row r="52" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
       <c r="B52" s="5"/>
       <c r="C52" s="13"/>
@@ -6099,7 +6574,7 @@
       </c>
       <c r="H52" s="5"/>
     </row>
-    <row r="53" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
       <c r="B53" s="5"/>
       <c r="C53" s="13">
@@ -6124,7 +6599,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
       <c r="B54" s="5"/>
       <c r="C54" s="13"/>
@@ -6136,7 +6611,7 @@
       </c>
       <c r="H54" s="5"/>
     </row>
-    <row r="55" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
       <c r="B55" s="5"/>
       <c r="C55" s="13">
@@ -6161,254 +6636,372 @@
         <v>94</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
       <c r="B56" s="5"/>
       <c r="C56" s="13">
         <v>3.6</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>3</v>
+        <v>194</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="13"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="13">
+        <v>3.7</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="13"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="13">
+        <v>3.8</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="E58" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="I58" s="25"/>
+    </row>
+    <row r="59" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="13"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="13">
+        <v>3.9</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="13"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="I60" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="J60" s="25" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="13"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+    </row>
+    <row r="62" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A62" s="18">
+        <v>4</v>
+      </c>
+      <c r="B62" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="H56" s="5" t="s">
+      <c r="C62" s="18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D62" s="19" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A57" s="18">
-        <v>4</v>
-      </c>
-      <c r="B57" s="19" t="s">
+      <c r="E62" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C57" s="18">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D57" s="19" t="s">
+      <c r="F62" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="G62" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H63" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="G57" s="19" t="s">
+    </row>
+    <row r="64" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="I65" s="20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G66" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="H57" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="18"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H58" s="20" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="18"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H59" s="20" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="18"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="H60" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="I60" s="20" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="18"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="F61" s="19" t="s">
+      <c r="H66" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="G61" s="19" t="s">
+    </row>
+    <row r="67" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E67" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="H61" s="20" t="s">
+      <c r="F67" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H67" s="21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E68" s="19" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18">
-        <v>4.3</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="G62" s="19" t="s">
+      <c r="F68" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="H62" s="21" t="s">
+      <c r="G68" s="19" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="18"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="F63" s="19" t="s">
+      <c r="H68" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="G63" s="19" t="s">
+    </row>
+    <row r="69" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="22">
+        <v>5</v>
+      </c>
+      <c r="B69" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="H63" s="21" t="s">
+      <c r="C69" s="22">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" s="23" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="22">
-        <v>5</v>
-      </c>
-      <c r="B64" s="23" t="s">
+      <c r="F69" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="C64" s="22">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D64" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E64" s="23" t="s">
+      <c r="G69" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="F64" s="23" t="s">
+      <c r="H69" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="G64" s="23" t="s">
+    </row>
+    <row r="70" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="22"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="22">
+        <v>5.2</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E70" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="H64" s="24" t="s">
+      <c r="F70" s="23" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="22"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="22">
-        <v>5.2</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E65" s="23" t="s">
+      <c r="G70" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="F65" s="23" t="s">
+      <c r="H70" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="G65" s="23" t="s">
+    </row>
+    <row r="71" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="22"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="22">
+        <v>5.3</v>
+      </c>
+      <c r="D71" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E71" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="H65" s="24" t="s">
+      <c r="F71" s="23" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="22"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="22">
-        <v>5.3</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E66" s="23" t="s">
+      <c r="G71" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="F66" s="23" t="s">
+      <c r="H71" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="G66" s="23" t="s">
+    </row>
+    <row r="72" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="22"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="22">
+        <v>5.4</v>
+      </c>
+      <c r="D72" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E72" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="H66" s="24" t="s">
+      <c r="F72" s="23" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="22"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="22">
-        <v>5.4</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E67" s="23" t="s">
+      <c r="G72" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="F67" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="G67" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="H67" s="23"/>
+      <c r="H72" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6476,19 +7069,29 @@
     <hyperlink ref="I53" r:id="rId54" display="Wireframes\0074RenterE-BikeBookingInsuranceDetails.png" xr:uid="{236BB8F4-9009-4592-A58E-E1E6F103B0E6}"/>
     <hyperlink ref="H55" r:id="rId55" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{5B52867C-3CB9-4EF9-BE50-53D66F9CEDB3}"/>
     <hyperlink ref="I55" r:id="rId56" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{86A1D131-334C-4475-BFB6-4967A44E9E8D}"/>
-    <hyperlink ref="H57" r:id="rId57" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
-    <hyperlink ref="H58" r:id="rId58" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
-    <hyperlink ref="H59" r:id="rId59" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
-    <hyperlink ref="H60" r:id="rId60" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
-    <hyperlink ref="I60" r:id="rId61" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
-    <hyperlink ref="H61" r:id="rId62" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
-    <hyperlink ref="H62" r:id="rId63" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
-    <hyperlink ref="H63" r:id="rId64" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
-    <hyperlink ref="H64" r:id="rId65" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
-    <hyperlink ref="H65" r:id="rId66" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
-    <hyperlink ref="H66" r:id="rId67" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
+    <hyperlink ref="H62" r:id="rId57" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
+    <hyperlink ref="H63" r:id="rId58" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
+    <hyperlink ref="H64" r:id="rId59" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
+    <hyperlink ref="H65" r:id="rId60" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
+    <hyperlink ref="I65" r:id="rId61" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
+    <hyperlink ref="H66" r:id="rId62" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
+    <hyperlink ref="H67" r:id="rId63" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
+    <hyperlink ref="H68" r:id="rId64" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
+    <hyperlink ref="H69" r:id="rId65" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
+    <hyperlink ref="H70" r:id="rId66" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
+    <hyperlink ref="H71" r:id="rId67" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
+    <hyperlink ref="H56" r:id="rId68" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{7E7AF681-6F9A-482D-8330-EAD00257E278}"/>
+    <hyperlink ref="H57" r:id="rId69" display="Wireframes\0081RenterEmptyBookedBikesList.png" xr:uid="{9484AB55-3F32-46D6-8F93-D45237DBB860}"/>
+    <hyperlink ref="I57" r:id="rId70" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{13128FE5-E76F-4266-9070-B354B0DAF968}"/>
+    <hyperlink ref="I56" r:id="rId71" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{094BC338-3FB3-4C94-90A7-464241E43A1D}"/>
+    <hyperlink ref="H58" r:id="rId72" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{6C17913F-06BA-4577-A87C-DFC9DD517147}"/>
+    <hyperlink ref="H59" r:id="rId73" display="Wireframes\0083RenterBookedE-BikeCancellationOption.png" xr:uid="{82363B0C-51D5-424F-A079-0DB91BC58ABE}"/>
+    <hyperlink ref="I59" r:id="rId74" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{85335B64-FF95-4DE9-A0F7-9D4108A04163}"/>
+    <hyperlink ref="H60" r:id="rId75" display="Wireframes\0084RenterBookedE-BikeFeaturesOptions.png" xr:uid="{1417CCC4-8A62-49CB-9F5B-6A34DA7ECAC1}"/>
+    <hyperlink ref="I60" r:id="rId76" display="Wireframes\0085RenterBookedE-BikeFeaturest2Check.png" xr:uid="{49F0D8D6-6DF3-415B-B5AF-268D8F267D5A}"/>
+    <hyperlink ref="J60" r:id="rId77" display="Wireframes\0086RenterBookedE-BikeRaiseIssue.png" xr:uid="{30B7E3EA-EE98-4724-BBF4-16849AF0B5C0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId68"/>
+  <pageSetup orientation="portrait" r:id="rId78"/>
 </worksheet>
 </file>
--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anodiam\desktop-tutorial\Micro2Move\BusinessAnalysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87EB565-289F-4933-8A9C-09B62121BBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB291EB-EF30-4675-8BCD-79E58A182979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4997,9 +4997,6 @@
     <t>0084RenterBookedE-BikeFeaturesOptions.png</t>
   </si>
   <si>
-    <t>0085RenterBookedE-BikeFeaturest2Check.png</t>
-  </si>
-  <si>
     <t>0086RenterBookedE-BikeRaiseIssue.png</t>
   </si>
   <si>
@@ -5093,6 +5090,9 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
+  </si>
+  <si>
+    <t>0085RenterBookedE-BikeFeaturestoCheck.png</t>
   </si>
 </sst>
 </file>
@@ -5200,7 +5200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -5223,12 +5223,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5305,11 +5318,14 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5616,31 +5632,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -5650,8 +5666,8 @@
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -6730,14 +6746,14 @@
       <c r="H59" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="I59" s="14" t="s">
+      <c r="I59" s="28" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="27" t="s">
+      <c r="C60" s="26" t="s">
         <v>210</v>
       </c>
       <c r="D60" s="5" t="s">
@@ -6750,23 +6766,23 @@
         <v>211</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H60" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="I60" s="25" t="s">
+      <c r="I60" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="J60" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="J60" s="25" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="27" t="s">
-        <v>216</v>
+      <c r="C61" s="26" t="s">
+        <v>215</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -7088,8 +7104,8 @@
     <hyperlink ref="H59" r:id="rId73" display="Wireframes\0083RenterBookedE-BikeCancellationOption.png" xr:uid="{82363B0C-51D5-424F-A079-0DB91BC58ABE}"/>
     <hyperlink ref="I59" r:id="rId74" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{85335B64-FF95-4DE9-A0F7-9D4108A04163}"/>
     <hyperlink ref="H60" r:id="rId75" display="Wireframes\0084RenterBookedE-BikeFeaturesOptions.png" xr:uid="{1417CCC4-8A62-49CB-9F5B-6A34DA7ECAC1}"/>
-    <hyperlink ref="I60" r:id="rId76" display="Wireframes\0085RenterBookedE-BikeFeaturest2Check.png" xr:uid="{49F0D8D6-6DF3-415B-B5AF-268D8F267D5A}"/>
-    <hyperlink ref="J60" r:id="rId77" display="Wireframes\0086RenterBookedE-BikeRaiseIssue.png" xr:uid="{30B7E3EA-EE98-4724-BBF4-16849AF0B5C0}"/>
+    <hyperlink ref="J60" r:id="rId76" display="Wireframes\0086RenterBookedE-BikeRaiseIssue.png" xr:uid="{30B7E3EA-EE98-4724-BBF4-16849AF0B5C0}"/>
+    <hyperlink ref="I60" r:id="rId77" display="Wireframes\0085RenterBookedE-BikeFeaturestoCheck.png" xr:uid="{F9969BA9-82C2-402D-9D9A-018A50EB72C2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId78"/>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB291EB-EF30-4675-8BCD-79E58A182979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D60F246-F327-4653-805B-C182E6AD0A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="231">
   <si>
     <t>As a</t>
   </si>
@@ -4942,6 +4942,139 @@
     <t>3.10</t>
   </si>
   <si>
+    <t>0084RenterBookedE-BikeFeaturesOptions.png</t>
+  </si>
+  <si>
+    <t>0086RenterBookedE-BikeRaiseIssue.png</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be able to check whether all the desired features are available for my selected E-bike. If not, I can raise an issue by clicking on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raise Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.  I should be able to see the screen for raising the issue where I can describe it and upload relevant image for the same. I may also choose to ignore the issue and click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ignore Issue, Go Back </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">option to reach the  E-bike's profile screen with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accept E-bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>0085RenterBookedE-BikeFeaturestoCheck.png</t>
+  </si>
+  <si>
+    <t>Renter who is currently riding their booked e-bike</t>
+  </si>
+  <si>
+    <t>See an utility interface of my booked e-bike</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">check the features of the E-bike selected by clicking on the e-bike features link before I choose to click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accept E-bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab or raise an issue</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">I can view all the features of that E-bike and check whether the </t>
     </r>
@@ -4964,135 +5097,41 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> is on for all of them. If any of them is not available, I can raise an issue, otherwise accept the e-bike.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">check the features of the E-bike selected by clicking on the e-bike features link before I choose to click on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accept E-bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab or raise an issue. </t>
-    </r>
-  </si>
-  <si>
-    <t>0084RenterBookedE-BikeFeaturesOptions.png</t>
-  </si>
-  <si>
-    <t>0086RenterBookedE-BikeRaiseIssue.png</t>
-  </si>
-  <si>
-    <t>3.11</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to check whether all the desired features are available for my selected E-bike. If not, I can raise an issue by clicking on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Raise Issue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.  I should be able to see the screen for raising the issue where I can describe it and upload relevant image for the same. I may also choose to ignore the issue and click on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Ignore Issue, Go Back </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">option to reach the  E-bike's profile screen with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accept E-bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> option</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>0085RenterBookedE-BikeFeaturestoCheck.png</t>
+      <t xml:space="preserve"> is on for all of them. If any of them is not available, I can raise an issue, otherwise accept the e-bike</t>
+    </r>
+  </si>
+  <si>
+    <t>0087RenterE-BikeCurrentBooking.png</t>
+  </si>
+  <si>
+    <t>0088RenterE-BikeCurrentBookingReportIncident.png</t>
+  </si>
+  <si>
+    <t>0089.0RenterE-BikeCurrentBookingClaimInsurance.png</t>
+  </si>
+  <si>
+    <t>I can view details of my booked e-bike, Owner's profile, Insurance details and claiming CTA, e-bike features checklist and report any incident with the e-bike I am riding</t>
+  </si>
+  <si>
+    <t>3.12</t>
+  </si>
+  <si>
+    <t>See an interface to return my booked e-bike (COULD BE SAME WITH USER STORY 3.11)</t>
+  </si>
+  <si>
+    <t>I can return the e-bike after my ride</t>
+  </si>
+  <si>
+    <t>0089.1RenterE-BikeReturn.png</t>
+  </si>
+  <si>
+    <t>0089.2RenterE-BikeReturn.png</t>
+  </si>
+  <si>
+    <t>See an option to continue riding or cancel the booking</t>
+  </si>
+  <si>
+    <t>I can choose whether I want to cancel prematurely or continue riding</t>
   </si>
 </sst>
 </file>
@@ -5138,7 +5177,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5199,6 +5238,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -5241,7 +5286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5321,10 +5366,13 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5617,7 +5665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="9" customWidth="1"/>
@@ -5632,31 +5680,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="28" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -5666,8 +5714,8 @@
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -6723,7 +6771,6 @@
       <c r="H58" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="I58" s="25"/>
     </row>
     <row r="59" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
@@ -6746,7 +6793,7 @@
       <c r="H59" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="I59" s="28" t="s">
+      <c r="I59" s="27" t="s">
         <v>202</v>
       </c>
     </row>
@@ -6760,93 +6807,117 @@
         <v>209</v>
       </c>
       <c r="E60" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="J60" s="14" t="s">
         <v>212</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="J60" s="14" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="5"/>
       <c r="C61" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+        <v>213</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>223</v>
+      </c>
       <c r="G61" s="5"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="25"/>
-      <c r="J61" s="25"/>
-    </row>
-    <row r="62" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A62" s="18">
+      <c r="H61" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="J61" s="14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="13"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="I62" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="J62" s="29"/>
+    </row>
+    <row r="63" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="13"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G63" s="5"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="29"/>
+    </row>
+    <row r="64" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A64" s="18">
         <v>4</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B64" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="C62" s="18">
+      <c r="C64" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D64" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="E64" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F64" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="G64" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="H62" s="20" t="s">
+      <c r="H64" s="20" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="18"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="H63" s="20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H64" s="20" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="19"/>
       <c r="C65" s="18"/>
@@ -6854,170 +6925,198 @@
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
       <c r="G65" s="19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="I65" s="20" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="19"/>
-      <c r="C66" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="F66" s="19" t="s">
-        <v>156</v>
-      </c>
+      <c r="C66" s="18"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
       <c r="G66" s="19" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18">
-        <v>4.3</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>161</v>
-      </c>
+      <c r="B67" s="19"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
       <c r="G67" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="H67" s="21" t="s">
-        <v>163</v>
+        <v>151</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="I67" s="20" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
+      <c r="B68" s="19"/>
       <c r="C68" s="18">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>144</v>
       </c>
       <c r="E68" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G68" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="H68" s="20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G69" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H69" s="21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E70" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F68" s="19" t="s">
+      <c r="F70" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="G68" s="19" t="s">
+      <c r="G70" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="H68" s="21" t="s">
+      <c r="H70" s="21" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="22">
+    <row r="71" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="22">
         <v>5</v>
       </c>
-      <c r="B69" s="23" t="s">
+      <c r="B71" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="C69" s="22">
+      <c r="C71" s="22">
         <v>5.0999999999999996</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E69" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="F69" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="G69" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="H69" s="24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A70" s="22"/>
-      <c r="B70" s="23"/>
-      <c r="C70" s="22">
-        <v>5.2</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="G70" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H70" s="24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="22"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="22">
-        <v>5.3</v>
       </c>
       <c r="D71" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F71" s="23" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="G71" s="23" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="22"/>
       <c r="B72" s="23"/>
       <c r="C72" s="22">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="D72" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E72" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G72" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H72" s="24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="22"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="22">
+        <v>5.3</v>
+      </c>
+      <c r="D73" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="G73" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="H73" s="24" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="22"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="22">
+        <v>5.4</v>
+      </c>
+      <c r="D74" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E74" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="F72" s="23" t="s">
+      <c r="F74" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="23" t="s">
+      <c r="G74" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="H72" s="23"/>
+      <c r="H74" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -7085,17 +7184,17 @@
     <hyperlink ref="I53" r:id="rId54" display="Wireframes\0074RenterE-BikeBookingInsuranceDetails.png" xr:uid="{236BB8F4-9009-4592-A58E-E1E6F103B0E6}"/>
     <hyperlink ref="H55" r:id="rId55" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{5B52867C-3CB9-4EF9-BE50-53D66F9CEDB3}"/>
     <hyperlink ref="I55" r:id="rId56" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{86A1D131-334C-4475-BFB6-4967A44E9E8D}"/>
-    <hyperlink ref="H62" r:id="rId57" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
-    <hyperlink ref="H63" r:id="rId58" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
-    <hyperlink ref="H64" r:id="rId59" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
-    <hyperlink ref="H65" r:id="rId60" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
-    <hyperlink ref="I65" r:id="rId61" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
-    <hyperlink ref="H66" r:id="rId62" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
-    <hyperlink ref="H67" r:id="rId63" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
-    <hyperlink ref="H68" r:id="rId64" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
-    <hyperlink ref="H69" r:id="rId65" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
-    <hyperlink ref="H70" r:id="rId66" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
-    <hyperlink ref="H71" r:id="rId67" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
+    <hyperlink ref="H64" r:id="rId57" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
+    <hyperlink ref="H65" r:id="rId58" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
+    <hyperlink ref="H66" r:id="rId59" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
+    <hyperlink ref="H67" r:id="rId60" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
+    <hyperlink ref="I67" r:id="rId61" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
+    <hyperlink ref="H68" r:id="rId62" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
+    <hyperlink ref="H69" r:id="rId63" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
+    <hyperlink ref="H70" r:id="rId64" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
+    <hyperlink ref="H71" r:id="rId65" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
+    <hyperlink ref="H72" r:id="rId66" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
+    <hyperlink ref="H73" r:id="rId67" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
     <hyperlink ref="H56" r:id="rId68" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{7E7AF681-6F9A-482D-8330-EAD00257E278}"/>
     <hyperlink ref="H57" r:id="rId69" display="Wireframes\0081RenterEmptyBookedBikesList.png" xr:uid="{9484AB55-3F32-46D6-8F93-D45237DBB860}"/>
     <hyperlink ref="I57" r:id="rId70" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{13128FE5-E76F-4266-9070-B354B0DAF968}"/>
@@ -7106,8 +7205,13 @@
     <hyperlink ref="H60" r:id="rId75" display="Wireframes\0084RenterBookedE-BikeFeaturesOptions.png" xr:uid="{1417CCC4-8A62-49CB-9F5B-6A34DA7ECAC1}"/>
     <hyperlink ref="J60" r:id="rId76" display="Wireframes\0086RenterBookedE-BikeRaiseIssue.png" xr:uid="{30B7E3EA-EE98-4724-BBF4-16849AF0B5C0}"/>
     <hyperlink ref="I60" r:id="rId77" display="Wireframes\0085RenterBookedE-BikeFeaturestoCheck.png" xr:uid="{F9969BA9-82C2-402D-9D9A-018A50EB72C2}"/>
+    <hyperlink ref="H61" r:id="rId78" display="Wireframes\0087RenterE-BikeCurrentBooking.png" xr:uid="{68398916-0808-429C-9063-0EF289E767C5}"/>
+    <hyperlink ref="I61" r:id="rId79" display="Wireframes\0088RenterE-BikeCurrentBookingReportIncident.png" xr:uid="{E211B067-0080-48BD-890A-3D5068865B67}"/>
+    <hyperlink ref="J61" r:id="rId80" display="Wireframes\0089.0RenterE-BikeCurrentBookingClaimInsurance.png" xr:uid="{5C8F6FAD-A9FF-4A4E-80C0-AB167AB0B419}"/>
+    <hyperlink ref="H62" r:id="rId81" display="Wireframes\0089.1RenterE-BikeReturn.png" xr:uid="{206F761D-8635-4C7C-A269-78867120C327}"/>
+    <hyperlink ref="I62" r:id="rId82" display="Wireframes\0089.2RenterE-BikeReturn.png" xr:uid="{B0CC76A8-63D9-48EE-8490-F84DE9F3F22A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId78"/>
+  <pageSetup orientation="portrait" r:id="rId83"/>
 </worksheet>
 </file>
--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D60F246-F327-4653-805B-C182E6AD0A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F38916-7ADD-4189-917B-ABF179D3ED32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15684" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="233">
   <si>
     <t>As a</t>
   </si>
@@ -4394,9 +4394,6 @@
     </r>
   </si>
   <si>
-    <t>If no Matching e-bikes are found, I must see a proper message. (No E-Bikes are found. Consider increasing your budget.)</t>
-  </si>
-  <si>
     <t>If one or more bikes are found matching my filters, the cheapest bike must be showed on top with larger image and details. The rest of the bikes must be showed as a list, in ascending order of price (cheapest &gt; costliest)</t>
   </si>
   <si>
@@ -4708,6 +4705,92 @@
     </r>
   </si>
   <si>
+    <t>0082RenterBookedE-BikeOptions.png</t>
+  </si>
+  <si>
+    <t>I can view the cancellation policy and options to confirm or not cancel</t>
+  </si>
+  <si>
+    <t>I can view the options for each listing on the E-bike profile page.</t>
+  </si>
+  <si>
+    <t>0083RenterBookedE-BikeCancellationOption.png</t>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <t>0084RenterBookedE-BikeFeaturesOptions.png</t>
+  </si>
+  <si>
+    <t>0086RenterBookedE-BikeRaiseIssue.png</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <t>0085RenterBookedE-BikeFeaturestoCheck.png</t>
+  </si>
+  <si>
+    <t>Renter who is currently riding their booked e-bike</t>
+  </si>
+  <si>
+    <t>See an utility interface of my booked e-bike</t>
+  </si>
+  <si>
+    <t>0087RenterE-BikeCurrentBooking.png</t>
+  </si>
+  <si>
+    <t>0088RenterE-BikeCurrentBookingReportIncident.png</t>
+  </si>
+  <si>
+    <t>0089.0RenterE-BikeCurrentBookingClaimInsurance.png</t>
+  </si>
+  <si>
+    <t>3.12</t>
+  </si>
+  <si>
+    <t>I can return the e-bike after my ride</t>
+  </si>
+  <si>
+    <t>0089.2RenterE-BikeReturn.png</t>
+  </si>
+  <si>
+    <t>I can choose whether I want to cancel prematurely or continue riding</t>
+  </si>
+  <si>
+    <t>See an interface to return my booked e-bike</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If no Matching e-bikes are found, I must see a proper </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> message. (No E-Bikes are found. Consider increasing your budget.)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">I must be navigated to the options for each E-bike listed, such as </t>
     </r>
@@ -4720,7 +4803,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ViewOwner's Profile</t>
+      <t>View Owner's Profile</t>
     </r>
     <r>
       <rPr>
@@ -4766,44 +4849,55 @@
     </r>
   </si>
   <si>
-    <t>0082RenterBookedE-BikeOptions.png</t>
-  </si>
-  <si>
-    <t>renter who has clicked on one of the listed options</t>
-  </si>
-  <si>
-    <t>I can view the cancellation policy and options to confirm or not cancel</t>
-  </si>
-  <si>
-    <t>I can view the options for each listing on the E-bike profile page.</t>
-  </si>
-  <si>
-    <t>0083RenterBookedE-BikeCancellationOption.png</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be navigated to the options on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancellation Policy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> page to find the </t>
+    <r>
+      <t xml:space="preserve">press on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink from the E-bike profile page.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. I must be navigated to the options on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeCancellationOption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen to find the </t>
     </r>
     <r>
       <rPr>
@@ -4845,18 +4939,19 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">for the respective E-Bike listed. I should be getting the option to either </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>confirm</t>
+      <t xml:space="preserve">for the respective E-Bike.
+2. I must be getting the option to either </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Confirm</t>
     </r>
     <r>
       <rPr>
@@ -4887,7 +4982,29 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> option. If I click on </t>
+      <t xml:space="preserve"> option and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Read more </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">hyperlink to see the full cancellation policy.
+3. If I click on </t>
     </r>
     <r>
       <rPr>
@@ -4908,7 +5025,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> tab, I shall be able to proceed with cancellation and if I click on </t>
+      <t xml:space="preserve"> button, I must be able to proceed with cancellation and if I click on </t>
     </r>
     <r>
       <rPr>
@@ -4929,30 +5046,42 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> tab I should be navigated back to the E-bike's profile page. </t>
-    </r>
-  </si>
-  <si>
-    <t>press on the cancel booking option from the E-bike profile page.</t>
-  </si>
-  <si>
-    <t>renter who has selected his/her desired E-bike</t>
-  </si>
-  <si>
-    <t>3.10</t>
-  </si>
-  <si>
-    <t>0084RenterBookedE-BikeFeaturesOptions.png</t>
-  </si>
-  <si>
-    <t>0086RenterBookedE-BikeRaiseIssue.png</t>
-  </si>
-  <si>
-    <t>3.11</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I must be able to check whether all the desired features are available for my selected E-bike. If not, I can raise an issue by clicking on the </t>
+      <t xml:space="preserve"> button I should be navigated back to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen.</t>
+    </r>
+  </si>
+  <si>
+    <t>renter who is going to accept their booked E-bike</t>
+  </si>
+  <si>
+    <t>check the working features of the E-bike, Insurance details before I choose to accept or raise an issue</t>
+  </si>
+  <si>
+    <t>I can view all the features of that E-bike and check whether everything is working fine. If any of them is not available, I can raise an issue, otherwise accept the e-bike</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. I must be able to check whether all the desired features are available and working for my selected E-bike. If not, I can raise an issue by clicking on the </t>
     </r>
     <r>
       <rPr>
@@ -4973,7 +5102,50 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> tab.  I should be able to see the screen for raising the issue where I can describe it and upload relevant image for the same. I may also choose to ignore the issue and click on </t>
+      <t xml:space="preserve"> button.  
+2. I must be able to see the screen for raising the issue by pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raise Issue + Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">where I can describe it and upload relevant image for the same. I may also choose to ignore the issue and click on </t>
     </r>
     <r>
       <rPr>
@@ -4994,28 +5166,28 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">option to reach the  E-bike's profile screen with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accept E-bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> option</t>
+      <t xml:space="preserve">button to go back to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
     </r>
     <r>
       <rPr>
@@ -5028,110 +5200,386 @@
       </rPr>
       <t>.</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>0085RenterBookedE-BikeFeaturestoCheck.png</t>
-  </si>
-  <si>
-    <t>Renter who is currently riding their booked e-bike</t>
-  </si>
-  <si>
-    <t>See an utility interface of my booked e-bike</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">check the features of the E-bike selected by clicking on the e-bike features link before I choose to click on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accept E-bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab or raise an issue</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can view all the features of that E-bike and check whether the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>toggle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is on for all of them. If any of them is not available, I can raise an issue, otherwise accept the e-bike</t>
-    </r>
-  </si>
-  <si>
-    <t>0087RenterE-BikeCurrentBooking.png</t>
-  </si>
-  <si>
-    <t>0088RenterE-BikeCurrentBookingReportIncident.png</t>
-  </si>
-  <si>
-    <t>0089.0RenterE-BikeCurrentBookingClaimInsurance.png</t>
-  </si>
-  <si>
-    <t>I can view details of my booked e-bike, Owner's profile, Insurance details and claiming CTA, e-bike features checklist and report any incident with the e-bike I am riding</t>
-  </si>
-  <si>
-    <t>3.12</t>
-  </si>
-  <si>
-    <t>See an interface to return my booked e-bike (COULD BE SAME WITH USER STORY 3.11)</t>
-  </si>
-  <si>
-    <t>I can return the e-bike after my ride</t>
-  </si>
-  <si>
-    <t>0089.1RenterE-BikeReturn.png</t>
-  </si>
-  <si>
-    <t>0089.2RenterE-BikeReturn.png</t>
-  </si>
-  <si>
-    <t>See an option to continue riding or cancel the booking</t>
-  </si>
-  <si>
-    <t>I can choose whether I want to cancel prematurely or continue riding</t>
+  </si>
+  <si>
+    <t>I can view details of my booked e-bike, Owner's profile, Insurance details and claiming CTA, e-bike features checklist, report any incident with the e-bike I am riding and return option</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. I must be able to see the following hyperlinks on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeCurrentBooking </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e-bike features</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Report an Incident</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Return an E-Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button.
+2. I must see an interface to upload image and describe the incident in details with a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Report</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button for reporting it, a button for dialling emergency helpline and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Make an Insurance Claim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeCurrentBookingReportIncident </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen, if I click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Report an Incident </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">hyperlink on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen.
+3. I must be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeCurrentBookingClaimInsurance </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen where I can read the full insurance claim policy and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Initiate Claim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button for starting the process.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeReturn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen where I can click and submit the current image of E-bike, rate my experience and leave a comment before returning the bike by pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Return </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button</t>
+    </r>
+  </si>
+  <si>
+    <t>See an option to continue riding or cancel the booking before booking duration ends</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I must see a modal to choose between </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Continue Riding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> buttons.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5245,7 +5693,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -5279,6 +5727,19 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -5360,19 +5821,19 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6534,7 +6995,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="H46" s="5"/>
     </row>
@@ -6546,7 +7007,7 @@
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>97</v>
@@ -6574,7 +7035,7 @@
         <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>98</v>
@@ -6583,7 +7044,7 @@
         <v>129</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="I49" s="14" t="s">
         <v>99</v>
@@ -6622,7 +7083,7 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H51" s="5"/>
     </row>
@@ -6707,16 +7168,16 @@
         <v>3.6</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>197</v>
-      </c>
       <c r="G56" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H56" s="14" t="s">
         <v>94</v>
@@ -6732,19 +7193,19 @@
         <v>3.7</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E57" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="H57" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>199</v>
       </c>
       <c r="I57" s="14" t="s">
         <v>43</v>
@@ -6757,139 +7218,149 @@
         <v>3.8</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E58" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H58" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="H58" s="14" t="s">
-        <v>202</v>
-      </c>
     </row>
-    <row r="59" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
       <c r="B59" s="5"/>
       <c r="C59" s="13">
         <v>3.9</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H59" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="I59" s="27" t="s">
-        <v>202</v>
+      <c r="I59" s="26" t="s">
+        <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="26" t="s">
-        <v>210</v>
+      <c r="C60" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="26" t="s">
+      <c r="C61" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="J61" s="14" t="s">
         <v>213</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G61" s="5"/>
-      <c r="H61" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="I61" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="26" t="s">
-        <v>224</v>
+      <c r="C62" s="25" t="s">
+        <v>214</v>
       </c>
       <c r="D62" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="I62" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G62" s="5"/>
-      <c r="H62" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="J62" s="29"/>
+      <c r="J62" s="27"/>
     </row>
     <row r="63" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
       <c r="B63" s="5"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="5"/>
+      <c r="C63" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>209</v>
+      </c>
       <c r="E63" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="G63" s="5"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="25"/>
-      <c r="J63" s="29"/>
+        <v>217</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H63" s="27"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="27"/>
     </row>
     <row r="64" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="18">
@@ -6913,7 +7384,7 @@
       <c r="G64" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="H64" s="20" t="s">
+      <c r="H64" s="29" t="s">
         <v>51</v>
       </c>
     </row>
@@ -7177,39 +7648,39 @@
     <hyperlink ref="H45" r:id="rId47" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{E2F540E0-19F6-4F94-A0A2-3BC06D68C587}"/>
     <hyperlink ref="H47" r:id="rId48" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{692C4001-F76C-4868-ADBB-B6860829A5DB}"/>
     <hyperlink ref="I49" r:id="rId49" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{927E8FB1-B6B7-4953-9C69-3804D1E25F6E}"/>
-    <hyperlink ref="H49" r:id="rId50" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{4FFB3AB2-680C-4078-8555-E258845D732F}"/>
-    <hyperlink ref="I50" r:id="rId51" display="Wireframes\0075RenterE-BikeBooking-SelectedBike'sOwnerDetails.png" xr:uid="{9A2FCA9B-F158-47F1-8E82-1C4F3E573697}"/>
-    <hyperlink ref="H50" r:id="rId52" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{BC83D10E-8EDE-451A-8B92-5C76042094C4}"/>
-    <hyperlink ref="H53" r:id="rId53" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{C89065FA-D199-44A4-8F21-6A5784EF30B0}"/>
-    <hyperlink ref="I53" r:id="rId54" display="Wireframes\0074RenterE-BikeBookingInsuranceDetails.png" xr:uid="{236BB8F4-9009-4592-A58E-E1E6F103B0E6}"/>
-    <hyperlink ref="H55" r:id="rId55" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{5B52867C-3CB9-4EF9-BE50-53D66F9CEDB3}"/>
-    <hyperlink ref="I55" r:id="rId56" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{86A1D131-334C-4475-BFB6-4967A44E9E8D}"/>
-    <hyperlink ref="H64" r:id="rId57" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
-    <hyperlink ref="H65" r:id="rId58" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
-    <hyperlink ref="H66" r:id="rId59" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
-    <hyperlink ref="H67" r:id="rId60" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
-    <hyperlink ref="I67" r:id="rId61" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
-    <hyperlink ref="H68" r:id="rId62" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
-    <hyperlink ref="H69" r:id="rId63" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
-    <hyperlink ref="H70" r:id="rId64" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
-    <hyperlink ref="H71" r:id="rId65" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
-    <hyperlink ref="H72" r:id="rId66" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
-    <hyperlink ref="H73" r:id="rId67" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
-    <hyperlink ref="H56" r:id="rId68" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{7E7AF681-6F9A-482D-8330-EAD00257E278}"/>
-    <hyperlink ref="H57" r:id="rId69" display="Wireframes\0081RenterEmptyBookedBikesList.png" xr:uid="{9484AB55-3F32-46D6-8F93-D45237DBB860}"/>
-    <hyperlink ref="I57" r:id="rId70" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{13128FE5-E76F-4266-9070-B354B0DAF968}"/>
-    <hyperlink ref="I56" r:id="rId71" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{094BC338-3FB3-4C94-90A7-464241E43A1D}"/>
-    <hyperlink ref="H58" r:id="rId72" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{6C17913F-06BA-4577-A87C-DFC9DD517147}"/>
-    <hyperlink ref="H59" r:id="rId73" display="Wireframes\0083RenterBookedE-BikeCancellationOption.png" xr:uid="{82363B0C-51D5-424F-A079-0DB91BC58ABE}"/>
-    <hyperlink ref="I59" r:id="rId74" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{85335B64-FF95-4DE9-A0F7-9D4108A04163}"/>
-    <hyperlink ref="H60" r:id="rId75" display="Wireframes\0084RenterBookedE-BikeFeaturesOptions.png" xr:uid="{1417CCC4-8A62-49CB-9F5B-6A34DA7ECAC1}"/>
-    <hyperlink ref="J60" r:id="rId76" display="Wireframes\0086RenterBookedE-BikeRaiseIssue.png" xr:uid="{30B7E3EA-EE98-4724-BBF4-16849AF0B5C0}"/>
-    <hyperlink ref="I60" r:id="rId77" display="Wireframes\0085RenterBookedE-BikeFeaturestoCheck.png" xr:uid="{F9969BA9-82C2-402D-9D9A-018A50EB72C2}"/>
-    <hyperlink ref="H61" r:id="rId78" display="Wireframes\0087RenterE-BikeCurrentBooking.png" xr:uid="{68398916-0808-429C-9063-0EF289E767C5}"/>
-    <hyperlink ref="I61" r:id="rId79" display="Wireframes\0088RenterE-BikeCurrentBookingReportIncident.png" xr:uid="{E211B067-0080-48BD-890A-3D5068865B67}"/>
-    <hyperlink ref="J61" r:id="rId80" display="Wireframes\0089.0RenterE-BikeCurrentBookingClaimInsurance.png" xr:uid="{5C8F6FAD-A9FF-4A4E-80C0-AB167AB0B419}"/>
-    <hyperlink ref="H62" r:id="rId81" display="Wireframes\0089.1RenterE-BikeReturn.png" xr:uid="{206F761D-8635-4C7C-A269-78867120C327}"/>
-    <hyperlink ref="I62" r:id="rId82" display="Wireframes\0089.2RenterE-BikeReturn.png" xr:uid="{B0CC76A8-63D9-48EE-8490-F84DE9F3F22A}"/>
+    <hyperlink ref="I50" r:id="rId50" display="Wireframes\0075RenterE-BikeBooking-SelectedBike'sOwnerDetails.png" xr:uid="{9A2FCA9B-F158-47F1-8E82-1C4F3E573697}"/>
+    <hyperlink ref="H50" r:id="rId51" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{BC83D10E-8EDE-451A-8B92-5C76042094C4}"/>
+    <hyperlink ref="H53" r:id="rId52" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{C89065FA-D199-44A4-8F21-6A5784EF30B0}"/>
+    <hyperlink ref="I53" r:id="rId53" display="Wireframes\0074RenterE-BikeBookingInsuranceDetails.png" xr:uid="{236BB8F4-9009-4592-A58E-E1E6F103B0E6}"/>
+    <hyperlink ref="H55" r:id="rId54" display="Wireframes\0073RenterE-BikeBookingConfirmation.png" xr:uid="{5B52867C-3CB9-4EF9-BE50-53D66F9CEDB3}"/>
+    <hyperlink ref="I55" r:id="rId55" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{86A1D131-334C-4475-BFB6-4967A44E9E8D}"/>
+    <hyperlink ref="H64" r:id="rId56" display="Wireframes\0090ExploreMaps.png" xr:uid="{1F52D47C-1EE9-4451-BC73-73B2D1319BCF}"/>
+    <hyperlink ref="H65" r:id="rId57" display="Wireframes\0091ExploreMapsNavigation.png" xr:uid="{01BAC6CE-6772-4BD5-BEF0-40F6AB56814A}"/>
+    <hyperlink ref="H66" r:id="rId58" display="Wireframes\0092ExploreMapsNavigationFlow.png" xr:uid="{EFA6A95B-655F-4BB4-90A6-6A5DFAEF6DDF}"/>
+    <hyperlink ref="H67" r:id="rId59" display="Wireframes\0093ExploreMapsMoreOptions.png" xr:uid="{6F21C05B-B9BD-4029-BF9D-0EAEC14BE39C}"/>
+    <hyperlink ref="I67" r:id="rId60" display="Wireframes\0094ExploreMapsBikeLanes.png" xr:uid="{4DF82FA9-65A1-45D2-A325-40888D6BB945}"/>
+    <hyperlink ref="H68" r:id="rId61" display="Wireframes\0100ExploreInfo.png" xr:uid="{6BF6B4C0-A092-40C3-96BE-2D27C506ACBE}"/>
+    <hyperlink ref="H69" r:id="rId62" display="Wireframes\0110ExploreCommunityUpdates.png" xr:uid="{28C8B87B-E579-41D6-BA1B-9C56BFD0D9C6}"/>
+    <hyperlink ref="H70" r:id="rId63" display="Wireframes\0120ExploreAskAI.png" xr:uid="{00E60735-1291-4130-90F3-6479E733F08C}"/>
+    <hyperlink ref="H71" r:id="rId64" display="Wireframes\0130Profile.png" xr:uid="{A2492735-E160-4E0D-A15F-E31A041B3A77}"/>
+    <hyperlink ref="H72" r:id="rId65" display="Wireframes\0131ProfileCommunityActivity.png" xr:uid="{F1C770CB-B4B2-4E45-895C-D4F237CB790E}"/>
+    <hyperlink ref="H73" r:id="rId66" display="Wireframes\0132ProfileLessons.png" xr:uid="{1E5F89DA-088F-493C-815E-BBD9C2CD382C}"/>
+    <hyperlink ref="H56" r:id="rId67" display="Wireframes\0080RenterBookedBikesList.png" xr:uid="{7E7AF681-6F9A-482D-8330-EAD00257E278}"/>
+    <hyperlink ref="H57" r:id="rId68" display="Wireframes\0081RenterEmptyBookedBikesList.png" xr:uid="{9484AB55-3F32-46D6-8F93-D45237DBB860}"/>
+    <hyperlink ref="I57" r:id="rId69" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{13128FE5-E76F-4266-9070-B354B0DAF968}"/>
+    <hyperlink ref="I56" r:id="rId70" display="Wireframes\0070RenterE-BikeBookingFilter.png" xr:uid="{094BC338-3FB3-4C94-90A7-464241E43A1D}"/>
+    <hyperlink ref="H58" r:id="rId71" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{6C17913F-06BA-4577-A87C-DFC9DD517147}"/>
+    <hyperlink ref="H59" r:id="rId72" display="Wireframes\0083RenterBookedE-BikeCancellationOption.png" xr:uid="{82363B0C-51D5-424F-A079-0DB91BC58ABE}"/>
+    <hyperlink ref="I59" r:id="rId73" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{85335B64-FF95-4DE9-A0F7-9D4108A04163}"/>
+    <hyperlink ref="H60" r:id="rId74" display="Wireframes\0084RenterBookedE-BikeFeaturesOptions.png" xr:uid="{1417CCC4-8A62-49CB-9F5B-6A34DA7ECAC1}"/>
+    <hyperlink ref="J60" r:id="rId75" display="Wireframes\0086RenterBookedE-BikeRaiseIssue.png" xr:uid="{30B7E3EA-EE98-4724-BBF4-16849AF0B5C0}"/>
+    <hyperlink ref="I60" r:id="rId76" display="Wireframes\0085RenterBookedE-BikeFeaturestoCheck.png" xr:uid="{F9969BA9-82C2-402D-9D9A-018A50EB72C2}"/>
+    <hyperlink ref="H61" r:id="rId77" display="Wireframes\0087RenterE-BikeCurrentBooking.png" xr:uid="{68398916-0808-429C-9063-0EF289E767C5}"/>
+    <hyperlink ref="I61" r:id="rId78" display="Wireframes\0088RenterE-BikeCurrentBookingReportIncident.png" xr:uid="{E211B067-0080-48BD-890A-3D5068865B67}"/>
+    <hyperlink ref="J61" r:id="rId79" display="Wireframes\0089.0RenterE-BikeCurrentBookingClaimInsurance.png" xr:uid="{5C8F6FAD-A9FF-4A4E-80C0-AB167AB0B419}"/>
+    <hyperlink ref="I62" r:id="rId80" display="Wireframes\0089.2RenterE-BikeReturn.png" xr:uid="{B0CC76A8-63D9-48EE-8490-F84DE9F3F22A}"/>
+    <hyperlink ref="H49" r:id="rId81" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{004D529A-8054-4285-9CE5-6045BE219679}"/>
+    <hyperlink ref="H62" r:id="rId82" display="Wireframes\0087RenterE-BikeCurrentBooking.png" xr:uid="{1449AD15-1BB1-41AD-B6F1-A29D83D5A8BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId83"/>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F38916-7ADD-4189-917B-ABF179D3ED32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C84C4F9-06B2-4AF2-915B-BBCB58E8CDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15684" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -5830,11 +5830,11 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6141,31 +6141,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="29" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -6175,8 +6175,8 @@
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -7384,7 +7384,7 @@
       <c r="G64" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="H64" s="29" t="s">
+      <c r="H64" s="28" t="s">
         <v>51</v>
       </c>
     </row>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C84C4F9-06B2-4AF2-915B-BBCB58E8CDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B6ED89-5391-4C61-B3BD-2241EA4BAE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11664" yWindow="0" windowWidth="11472" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -4679,39 +4679,10 @@
     <t>0081RenterEmptyBookedBikesList.png</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">press on any of the options from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterBookedBikesList</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and check the options  </t>
-    </r>
-  </si>
-  <si>
     <t>0082RenterBookedE-BikeOptions.png</t>
   </si>
   <si>
     <t>I can view the cancellation policy and options to confirm or not cancel</t>
-  </si>
-  <si>
-    <t>I can view the options for each listing on the E-bike profile page.</t>
   </si>
   <si>
     <t>0083RenterBookedE-BikeCancellationOption.png</t>
@@ -5579,6 +5550,58 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> buttons.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press on any of the cards from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedBikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can view the options for each listing on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
     </r>
   </si>
 </sst>
@@ -6995,7 +7018,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H46" s="5"/>
     </row>
@@ -7221,16 +7244,16 @@
         <v>193</v>
       </c>
       <c r="E58" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H58" s="14" t="s">
         <v>199</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="H58" s="14" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="216" x14ac:dyDescent="0.3">
@@ -7243,100 +7266,100 @@
         <v>3</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F59" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H59" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>203</v>
-      </c>
       <c r="I59" s="26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="5"/>
       <c r="C60" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="J60" s="14" t="s">
         <v>204</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="J60" s="14" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="5"/>
       <c r="C61" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="E61" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H61" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="I61" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="H61" s="14" t="s">
+      <c r="J61" s="14" t="s">
         <v>211</v>
-      </c>
-      <c r="I61" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
       <c r="B62" s="5"/>
       <c r="C62" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="I62" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>216</v>
       </c>
       <c r="J62" s="27"/>
     </row>
@@ -7344,19 +7367,19 @@
       <c r="A63" s="13"/>
       <c r="B63" s="5"/>
       <c r="C63" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H63" s="27"/>
       <c r="I63" s="27"/>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B6ED89-5391-4C61-B3BD-2241EA4BAE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104E8A80-33B9-4E89-8425-095220006C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11664" yWindow="0" windowWidth="11472" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -4691,9 +4691,6 @@
     <t>3.10</t>
   </si>
   <si>
-    <t>0084RenterBookedE-BikeFeaturesOptions.png</t>
-  </si>
-  <si>
     <t>0086RenterBookedE-BikeRaiseIssue.png</t>
   </si>
   <si>
@@ -5603,6 +5600,9 @@
       </rPr>
       <t xml:space="preserve"> screen</t>
     </r>
+  </si>
+  <si>
+    <t>0084RenterBookedE-BikeOptions(onBookingStartDate).png</t>
   </si>
 </sst>
 </file>
@@ -7018,7 +7018,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H46" s="5"/>
     </row>
@@ -7244,13 +7244,13 @@
         <v>193</v>
       </c>
       <c r="E58" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>232</v>
-      </c>
       <c r="G58" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H58" s="14" t="s">
         <v>199</v>
@@ -7266,13 +7266,13 @@
         <v>3</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>200</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H59" s="14" t="s">
         <v>201</v>
@@ -7288,78 +7288,78 @@
         <v>202</v>
       </c>
       <c r="D60" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="F60" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="G60" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="H60" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="J60" s="14" t="s">
         <v>203</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="J60" s="14" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="5"/>
       <c r="C61" s="25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H61" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="H61" s="14" t="s">
+      <c r="I61" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="I61" s="14" t="s">
+      <c r="J61" s="14" t="s">
         <v>210</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
       <c r="B62" s="5"/>
       <c r="C62" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F62" s="5" t="s">
+      <c r="G62" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="I62" s="14" t="s">
         <v>213</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>214</v>
       </c>
       <c r="J62" s="27"/>
     </row>
@@ -7367,19 +7367,19 @@
       <c r="A63" s="13"/>
       <c r="B63" s="5"/>
       <c r="C63" s="25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E63" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="H63" s="27"/>
       <c r="I63" s="27"/>
@@ -7695,15 +7695,15 @@
     <hyperlink ref="H58" r:id="rId71" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{6C17913F-06BA-4577-A87C-DFC9DD517147}"/>
     <hyperlink ref="H59" r:id="rId72" display="Wireframes\0083RenterBookedE-BikeCancellationOption.png" xr:uid="{82363B0C-51D5-424F-A079-0DB91BC58ABE}"/>
     <hyperlink ref="I59" r:id="rId73" display="Wireframes\0082RenterBookedE-BikeOptions.png" xr:uid="{85335B64-FF95-4DE9-A0F7-9D4108A04163}"/>
-    <hyperlink ref="H60" r:id="rId74" display="Wireframes\0084RenterBookedE-BikeFeaturesOptions.png" xr:uid="{1417CCC4-8A62-49CB-9F5B-6A34DA7ECAC1}"/>
-    <hyperlink ref="J60" r:id="rId75" display="Wireframes\0086RenterBookedE-BikeRaiseIssue.png" xr:uid="{30B7E3EA-EE98-4724-BBF4-16849AF0B5C0}"/>
-    <hyperlink ref="I60" r:id="rId76" display="Wireframes\0085RenterBookedE-BikeFeaturestoCheck.png" xr:uid="{F9969BA9-82C2-402D-9D9A-018A50EB72C2}"/>
-    <hyperlink ref="H61" r:id="rId77" display="Wireframes\0087RenterE-BikeCurrentBooking.png" xr:uid="{68398916-0808-429C-9063-0EF289E767C5}"/>
-    <hyperlink ref="I61" r:id="rId78" display="Wireframes\0088RenterE-BikeCurrentBookingReportIncident.png" xr:uid="{E211B067-0080-48BD-890A-3D5068865B67}"/>
-    <hyperlink ref="J61" r:id="rId79" display="Wireframes\0089.0RenterE-BikeCurrentBookingClaimInsurance.png" xr:uid="{5C8F6FAD-A9FF-4A4E-80C0-AB167AB0B419}"/>
-    <hyperlink ref="I62" r:id="rId80" display="Wireframes\0089.2RenterE-BikeReturn.png" xr:uid="{B0CC76A8-63D9-48EE-8490-F84DE9F3F22A}"/>
-    <hyperlink ref="H49" r:id="rId81" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{004D529A-8054-4285-9CE5-6045BE219679}"/>
-    <hyperlink ref="H62" r:id="rId82" display="Wireframes\0087RenterE-BikeCurrentBooking.png" xr:uid="{1449AD15-1BB1-41AD-B6F1-A29D83D5A8BC}"/>
+    <hyperlink ref="J60" r:id="rId74" display="Wireframes\0086RenterBookedE-BikeRaiseIssue.png" xr:uid="{30B7E3EA-EE98-4724-BBF4-16849AF0B5C0}"/>
+    <hyperlink ref="I60" r:id="rId75" display="Wireframes\0085RenterBookedE-BikeFeaturestoCheck.png" xr:uid="{F9969BA9-82C2-402D-9D9A-018A50EB72C2}"/>
+    <hyperlink ref="H61" r:id="rId76" display="Wireframes\0087RenterE-BikeCurrentBooking.png" xr:uid="{68398916-0808-429C-9063-0EF289E767C5}"/>
+    <hyperlink ref="I61" r:id="rId77" display="Wireframes\0088RenterE-BikeCurrentBookingReportIncident.png" xr:uid="{E211B067-0080-48BD-890A-3D5068865B67}"/>
+    <hyperlink ref="J61" r:id="rId78" display="Wireframes\0089.0RenterE-BikeCurrentBookingClaimInsurance.png" xr:uid="{5C8F6FAD-A9FF-4A4E-80C0-AB167AB0B419}"/>
+    <hyperlink ref="I62" r:id="rId79" display="Wireframes\0089.2RenterE-BikeReturn.png" xr:uid="{B0CC76A8-63D9-48EE-8490-F84DE9F3F22A}"/>
+    <hyperlink ref="H49" r:id="rId80" display="Wireframes\0072RenterE-BikeBooking-BikeDetails.png" xr:uid="{004D529A-8054-4285-9CE5-6045BE219679}"/>
+    <hyperlink ref="H62" r:id="rId81" display="Wireframes\0087RenterE-BikeCurrentBooking.png" xr:uid="{1449AD15-1BB1-41AD-B6F1-A29D83D5A8BC}"/>
+    <hyperlink ref="H60" r:id="rId82" display="Wireframes\0084RenterBookedE-BikeOptions(onBookingStartDate).png" xr:uid="{0AC517E5-BD61-4CD2-B578-FB0FF4F742CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId83"/>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104E8A80-33B9-4E89-8425-095220006C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7042DDE-F20C-4EEB-87A5-034AFD03859A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2996,32 +2996,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">I must be able to see a list of matching e-bikes in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBooking-BikeDetails</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sorted in ascending order of price.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">press the </t>
     </r>
     <r>
@@ -5603,6 +5577,33 @@
   </si>
   <si>
     <t>0084RenterBookedE-BikeOptions(onBookingStartDate).png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. I must be able to see a list of matching e-bikes in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBooking-BikeDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sorted in ascending order of price.
+2. I must be able to see if the E-Bike is platform verified or not, signified by the presence of a verified badge.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6509,7 +6510,7 @@
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>15</v>
@@ -6745,7 +6746,7 @@
         <v>70</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>66</v>
@@ -6759,7 +6760,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H30" s="4"/>
     </row>
@@ -6977,11 +6978,11 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H44" s="12"/>
     </row>
-    <row r="45" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A45" s="13">
         <v>3</v>
       </c>
@@ -7001,7 +7002,7 @@
         <v>95</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="H45" s="14" t="s">
         <v>43</v>
@@ -7018,7 +7019,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H46" s="5"/>
     </row>
@@ -7030,7 +7031,7 @@
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>97</v>
@@ -7044,7 +7045,7 @@
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H48" s="14"/>
     </row>
@@ -7058,7 +7059,7 @@
         <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>98</v>
@@ -7083,19 +7084,19 @@
         <v>3</v>
       </c>
       <c r="E50" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="G50" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H50" s="14" t="s">
         <v>99</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7106,7 +7107,7 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H51" s="5"/>
     </row>
@@ -7118,7 +7119,7 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H52" s="5"/>
     </row>
@@ -7132,19 +7133,19 @@
         <v>3</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="H53" s="14" t="s">
         <v>99</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -7155,7 +7156,7 @@
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H54" s="5"/>
     </row>
@@ -7169,13 +7170,13 @@
         <v>3</v>
       </c>
       <c r="E55" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F55" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="H55" s="14" t="s">
         <v>99</v>
@@ -7191,16 +7192,16 @@
         <v>3.6</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="G56" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H56" s="14" t="s">
         <v>94</v>
@@ -7216,19 +7217,19 @@
         <v>3.7</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E57" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="H57" s="14" t="s">
         <v>197</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>198</v>
       </c>
       <c r="I57" s="14" t="s">
         <v>43</v>
@@ -7241,19 +7242,19 @@
         <v>3.8</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E58" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>231</v>
-      </c>
       <c r="G58" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="216" x14ac:dyDescent="0.3">
@@ -7266,100 +7267,100 @@
         <v>3</v>
       </c>
       <c r="E59" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="H59" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>201</v>
-      </c>
       <c r="I59" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="5"/>
       <c r="C60" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="J60" s="14" t="s">
         <v>202</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="J60" s="14" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="5"/>
       <c r="C61" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H61" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H61" s="14" t="s">
+      <c r="I61" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="I61" s="14" t="s">
+      <c r="J61" s="14" t="s">
         <v>209</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
       <c r="B62" s="5"/>
       <c r="C62" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F62" s="5" t="s">
+      <c r="G62" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="I62" s="14" t="s">
         <v>212</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>213</v>
       </c>
       <c r="J62" s="27"/>
     </row>
@@ -7367,19 +7368,19 @@
       <c r="A63" s="13"/>
       <c r="B63" s="5"/>
       <c r="C63" s="25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E63" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="H63" s="27"/>
       <c r="I63" s="27"/>
@@ -7390,22 +7391,22 @@
         <v>4</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C64" s="18">
         <v>4.0999999999999996</v>
       </c>
       <c r="D64" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="F64" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="F64" s="19" t="s">
-        <v>146</v>
-      </c>
       <c r="G64" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H64" s="28" t="s">
         <v>51</v>
@@ -7419,10 +7420,10 @@
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
       <c r="G65" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -7433,10 +7434,10 @@
       <c r="E66" s="19"/>
       <c r="F66" s="19"/>
       <c r="G66" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -7447,13 +7448,13 @@
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
       <c r="G67" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H67" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="H67" s="20" t="s">
+      <c r="I67" s="20" t="s">
         <v>152</v>
-      </c>
-      <c r="I67" s="20" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -7463,19 +7464,19 @@
         <v>4.2</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F68" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="G68" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="G68" s="19" t="s">
+      <c r="H68" s="20" t="s">
         <v>157</v>
-      </c>
-      <c r="H68" s="20" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -7485,19 +7486,19 @@
         <v>4.3</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F69" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G69" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="G69" s="19" t="s">
+      <c r="H69" s="21" t="s">
         <v>162</v>
-      </c>
-      <c r="H69" s="21" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -7507,19 +7508,19 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F70" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G70" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="G70" s="19" t="s">
+      <c r="H70" s="21" t="s">
         <v>165</v>
-      </c>
-      <c r="H70" s="21" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -7527,25 +7528,25 @@
         <v>5</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C71" s="22">
         <v>5.0999999999999996</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E71" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F71" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="F71" s="23" t="s">
+      <c r="G71" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="H71" s="24" t="s">
         <v>170</v>
-      </c>
-      <c r="H71" s="24" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -7555,19 +7556,19 @@
         <v>5.2</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E72" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="F72" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="F72" s="23" t="s">
+      <c r="G72" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="G72" s="23" t="s">
+      <c r="H72" s="24" t="s">
         <v>174</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -7577,19 +7578,19 @@
         <v>5.3</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E73" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="F73" s="23" t="s">
+      <c r="G73" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="G73" s="23" t="s">
+      <c r="H73" s="24" t="s">
         <v>178</v>
-      </c>
-      <c r="H73" s="24" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -7599,16 +7600,16 @@
         <v>5.4</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E74" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="F74" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="F74" s="23" t="s">
+      <c r="G74" s="23" t="s">
         <v>181</v>
-      </c>
-      <c r="G74" s="23" t="s">
-        <v>182</v>
       </c>
       <c r="H74" s="23"/>
     </row>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7042DDE-F20C-4EEB-87A5-034AFD03859A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8361249-CAAB-418D-8615-1E6359747304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="13044" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
@@ -3810,9 +3810,6 @@
     </r>
   </si>
   <si>
-    <t>I can see all the commnity updates</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">I must be able to see community updates (if any) screen, with </t>
     </r>
@@ -5604,6 +5601,9 @@
       <t xml:space="preserve"> sorted in ascending order of price.
 2. I must be able to see if the E-Bike is platform verified or not, signified by the presence of a verified badge.</t>
     </r>
+  </si>
+  <si>
+    <t>I can see all the community updates</t>
   </si>
 </sst>
 </file>
@@ -6510,7 +6510,7 @@
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>15</v>
@@ -6746,7 +6746,7 @@
         <v>70</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>66</v>
@@ -6760,7 +6760,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H30" s="4"/>
     </row>
@@ -6978,7 +6978,7 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H44" s="12"/>
     </row>
@@ -7002,7 +7002,7 @@
         <v>95</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H45" s="14" t="s">
         <v>43</v>
@@ -7019,7 +7019,7 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H46" s="5"/>
     </row>
@@ -7031,7 +7031,7 @@
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>97</v>
@@ -7045,7 +7045,7 @@
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H48" s="14"/>
     </row>
@@ -7059,7 +7059,7 @@
         <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>98</v>
@@ -7107,7 +7107,7 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H51" s="5"/>
     </row>
@@ -7192,16 +7192,16 @@
         <v>3.6</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="G56" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H56" s="14" t="s">
         <v>94</v>
@@ -7217,19 +7217,19 @@
         <v>3.7</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E57" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="H57" s="14" t="s">
         <v>196</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>197</v>
       </c>
       <c r="I57" s="14" t="s">
         <v>43</v>
@@ -7242,19 +7242,19 @@
         <v>3.8</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E58" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>230</v>
-      </c>
       <c r="G58" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="216" x14ac:dyDescent="0.3">
@@ -7267,100 +7267,100 @@
         <v>3</v>
       </c>
       <c r="E59" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="H59" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>200</v>
-      </c>
       <c r="I59" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="5"/>
       <c r="C60" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="J60" s="14" t="s">
         <v>201</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="J60" s="14" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="5"/>
       <c r="C61" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H61" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="H61" s="14" t="s">
+      <c r="I61" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="I61" s="14" t="s">
+      <c r="J61" s="14" t="s">
         <v>208</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
       <c r="B62" s="5"/>
       <c r="C62" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="F62" s="5" t="s">
+      <c r="G62" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="I62" s="14" t="s">
         <v>211</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>212</v>
       </c>
       <c r="J62" s="27"/>
     </row>
@@ -7368,19 +7368,19 @@
       <c r="A63" s="13"/>
       <c r="B63" s="5"/>
       <c r="C63" s="25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E63" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="H63" s="27"/>
       <c r="I63" s="27"/>
@@ -7492,13 +7492,13 @@
         <v>158</v>
       </c>
       <c r="F69" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G69" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="G69" s="19" t="s">
+      <c r="H69" s="21" t="s">
         <v>161</v>
-      </c>
-      <c r="H69" s="21" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
@@ -7514,13 +7514,13 @@
         <v>159</v>
       </c>
       <c r="F70" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="G70" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="G70" s="19" t="s">
+      <c r="H70" s="21" t="s">
         <v>164</v>
-      </c>
-      <c r="H70" s="21" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
@@ -7528,7 +7528,7 @@
         <v>5</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C71" s="22">
         <v>5.0999999999999996</v>
@@ -7537,16 +7537,16 @@
         <v>143</v>
       </c>
       <c r="E71" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="F71" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="F71" s="23" t="s">
+      <c r="G71" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="H71" s="24" t="s">
         <v>169</v>
-      </c>
-      <c r="H71" s="24" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -7559,16 +7559,16 @@
         <v>143</v>
       </c>
       <c r="E72" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="F72" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="F72" s="23" t="s">
+      <c r="G72" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="G72" s="23" t="s">
+      <c r="H72" s="24" t="s">
         <v>173</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -7581,16 +7581,16 @@
         <v>143</v>
       </c>
       <c r="E73" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="F73" s="23" t="s">
+      <c r="G73" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="G73" s="23" t="s">
+      <c r="H73" s="24" t="s">
         <v>177</v>
-      </c>
-      <c r="H73" s="24" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -7603,13 +7603,13 @@
         <v>143</v>
       </c>
       <c r="E74" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="F74" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="F74" s="23" t="s">
+      <c r="G74" s="23" t="s">
         <v>180</v>
-      </c>
-      <c r="G74" s="23" t="s">
-        <v>181</v>
       </c>
       <c r="H74" s="23"/>
     </row>

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -1,37 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANODIAM\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8361249-CAAB-418D-8615-1E6359747304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62B51B9-E1AF-48B3-862B-DC43C37F092F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="13044" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBacklog" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="264">
   <si>
     <t>As a</t>
   </si>
@@ -5604,13 +5593,135 @@
   </si>
   <si>
     <t>I can see all the community updates</t>
+  </si>
+  <si>
+    <t>Supplier Auth</t>
+  </si>
+  <si>
+    <t>Unregistered Product Owner</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>attempt to log in using my email and password</t>
+    </r>
+  </si>
+  <si>
+    <t>I can access the Supplier Portal</t>
+  </si>
+  <si>
+    <t>If I enter an email that is not registered in the system, I must see an error message: “Account not found. Please register to continue.” I must be given a clear Register button / hyperlink.</t>
+  </si>
+  <si>
+    <t>I can request access to the Supplier Portal</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>register my business details</t>
+    </r>
+  </si>
+  <si>
+    <t>I must be able to enter Store Name, Location, ABN, Email, Password, Owner/Manager Name and Phone Number. All fields must be mandatory. If any field is invalid, respective error messages must be shown on the same screen. If all details are valid, I must see a success message: “Thank you for registering! Admin will soon grant you access.”</t>
+  </si>
+  <si>
+    <t>If I enter valid credentials and my account status is Approved, I must be successfully logged in. If I have no existing fleet listings, I must be redirected to the “List Your First e-Bike Fleet” screen. The screen must display a large “+” button to add my first fleet. A welcome header must be visible.</t>
+  </si>
+  <si>
+    <t>Approved Product Owner with Existing Fleets</t>
+  </si>
+  <si>
+    <t>I want to log in using valid credentials</t>
+  </si>
+  <si>
+    <t>I can manage my existing e-bike fleets</t>
+  </si>
+  <si>
+    <t>If I enter valid credentials and I already have one or more fleets listed, I must be redirected to the “Your e-Bike Fleets” screen. I must see all my listed fleets with: Fleet Name, Image, Price per week, Category, Location and Quantity (Qty). I must see a “List Another Fleet” button at the bottom.</t>
+  </si>
+  <si>
+    <t>Fleet Management</t>
+  </si>
+  <si>
+    <t>Approved Product Owner (No Existing Fleets)</t>
+  </si>
+  <si>
+    <t>I want to add my first e-Bike fleet</t>
+  </si>
+  <si>
+    <t>I can make my bikes available for rental on Micro2Move</t>
+  </si>
+  <si>
+    <t>If I am a logged-in and approved Product Owner with no existing fleets, I must be redirected to the “List Your First e-Bike Fleet” screen. I must see a large “+” button to add my first fleet. When I press the “+” button, I must be navigated to the e-Bike Fleet creation form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved Product Owner </t>
+  </si>
+  <si>
+    <t>I want to open the side menu from the fleet screen</t>
+  </si>
+  <si>
+    <t>I can navigate to Manage Listing, Analytics, or Profile</t>
+  </si>
+  <si>
+    <t>If I tap on the three-dot menu icon from the Fleet screen, I must see a side menu panel open. The side menu must display the following options:1.ManageListing 2.Analytics 3.Profile. A close (X) icon must be visible at the top right corner. If I tap the close (X) icon, the menu must close and return to the previous screen.</t>
+  </si>
+  <si>
+    <t>I want to select “Manage Listing” from the side menu</t>
+  </si>
+  <si>
+    <t>If I tap on “Manage Listing”, I must be redirected to the Manage Listing screen.
+The Manage Listing option must be visually highlighted when selected.</t>
+  </si>
+  <si>
+    <t>I want to select “Analytics” from the side menu</t>
+  </si>
+  <si>
+    <t>I can view my fleet performance insights</t>
+  </si>
+  <si>
+    <t>I can edit or manage my fleet details</t>
+  </si>
+  <si>
+    <t>If I tap on “Analytics”, I must be redirected to the Analytics dashboard screen.
+The Analytics option must be visually highlighted when selected.</t>
+  </si>
+  <si>
+    <t>I want to select “Profile” from the side menu</t>
+  </si>
+  <si>
+    <t>I can view and manage my supplier profile</t>
+  </si>
+  <si>
+    <t>If I tap on “Profile”, I must be redirected to the Supplier Profile screen.
+The Profile option must be visually highlighted when selected</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5648,8 +5759,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5716,6 +5834,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -5771,7 +5901,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5859,6 +5989,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6150,13 +6316,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="9" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="6.33203125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="24" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.77734375" style="2" customWidth="1"/>
     <col min="7" max="7" width="40.44140625" style="2" customWidth="1"/>
@@ -7594,24 +7760,185 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="22"/>
-      <c r="B74" s="23"/>
-      <c r="C74" s="22">
+      <c r="A74" s="37"/>
+      <c r="B74" s="38"/>
+      <c r="C74" s="37">
         <v>5.4</v>
       </c>
-      <c r="D74" s="23" t="s">
+      <c r="D74" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="E74" s="23" t="s">
+      <c r="E74" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="F74" s="23" t="s">
+      <c r="F74" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="G74" s="23" t="s">
+      <c r="G74" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="H74" s="23"/>
+      <c r="H74" s="38"/>
+    </row>
+    <row r="75" spans="1:9" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="35"/>
+      <c r="C75" s="35"/>
+    </row>
+    <row r="76" spans="1:9" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="39">
+        <v>6</v>
+      </c>
+      <c r="B76" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" s="39">
+        <v>6.1</v>
+      </c>
+      <c r="D76" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="E76" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="F76" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="G76" s="40" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="30"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="30">
+        <v>6.2</v>
+      </c>
+      <c r="D77" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="E77" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="F77" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="G77" s="31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="30"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="32">
+        <v>7</v>
+      </c>
+      <c r="B79" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="C79" s="32">
+        <v>7.1</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="F79" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="G79" s="34" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="32"/>
+      <c r="B80" s="34"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="G80" s="34" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="32"/>
+      <c r="B81" s="34"/>
+      <c r="C81" s="32">
+        <v>7.2</v>
+      </c>
+      <c r="D81" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="F81" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="G81" s="34" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="32"/>
+      <c r="B82" s="34"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="F82" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="G82" s="34" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="32"/>
+      <c r="B83" s="34"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F83" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="G83" s="34" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="32"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="34"/>
+      <c r="E84" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="F84" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="G84" s="34" t="s">
+        <v>263</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/BusinessAnalysis/ProductBacklog.xlsx
+++ b/BusinessAnalysis/ProductBacklog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANODIAM\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62B51B9-E1AF-48B3-862B-DC43C37F092F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2A4C9D-4B33-4CE9-9326-2CB439A46A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="287">
   <si>
     <t>As a</t>
   </si>
@@ -5651,9 +5651,6 @@
     <t>Approved Product Owner with Existing Fleets</t>
   </si>
   <si>
-    <t>I want to log in using valid credentials</t>
-  </si>
-  <si>
     <t>I can manage my existing e-bike fleets</t>
   </si>
   <si>
@@ -5666,9 +5663,6 @@
     <t>Approved Product Owner (No Existing Fleets)</t>
   </si>
   <si>
-    <t>I want to add my first e-Bike fleet</t>
-  </si>
-  <si>
     <t>I can make my bikes available for rental on Micro2Move</t>
   </si>
   <si>
@@ -5678,25 +5672,16 @@
     <t xml:space="preserve">Approved Product Owner </t>
   </si>
   <si>
-    <t>I want to open the side menu from the fleet screen</t>
-  </si>
-  <si>
     <t>I can navigate to Manage Listing, Analytics, or Profile</t>
   </si>
   <si>
     <t>If I tap on the three-dot menu icon from the Fleet screen, I must see a side menu panel open. The side menu must display the following options:1.ManageListing 2.Analytics 3.Profile. A close (X) icon must be visible at the top right corner. If I tap the close (X) icon, the menu must close and return to the previous screen.</t>
-  </si>
-  <si>
-    <t>I want to select “Manage Listing” from the side menu</t>
   </si>
   <si>
     <t>If I tap on “Manage Listing”, I must be redirected to the Manage Listing screen.
 The Manage Listing option must be visually highlighted when selected.</t>
   </si>
   <si>
-    <t>I want to select “Analytics” from the side menu</t>
-  </si>
-  <si>
     <t>I can view my fleet performance insights</t>
   </si>
   <si>
@@ -5707,14 +5692,267 @@
 The Analytics option must be visually highlighted when selected.</t>
   </si>
   <si>
-    <t>I want to select “Profile” from the side menu</t>
-  </si>
-  <si>
     <t>I can view and manage my supplier profile</t>
   </si>
   <si>
     <t>If I tap on “Profile”, I must be redirected to the Supplier Profile screen.
 The Profile option must be visually highlighted when selected</t>
+  </si>
+  <si>
+    <t>Supplier Profile Management</t>
+  </si>
+  <si>
+    <t>Approved Product Owner</t>
+  </si>
+  <si>
+    <t>I can see my registered business information</t>
+  </si>
+  <si>
+    <t>I must see: Store Name (Header), Manager Name with profile image, Location, ABN, Email (clickable) and Phone Number. Profile information must be fetched dynamically from database. Email must open default mail client when clicked. Profile screen must load within acceptable performance time.</t>
+  </si>
+  <si>
+    <t>My business profile looks professional</t>
+  </si>
+  <si>
+    <t>I must be able to tap camera icon on profile image. I must be able to: Capture new image. Image must update immediately after upload. Only valid image formats allowed. Maximum size validation must apply.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>upload or change my profile image</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>I want to view</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> my store and manager details</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Profile” from the side menu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Analytics” from the side menu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Manage Listing” from the side menu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add my first e-Bike fleet</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>I want to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> log in using valid credentials</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>open the side menu from the fleet screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>upload or update my store banner image</t>
+    </r>
+  </si>
+  <si>
+    <t>My store branding is visible.</t>
+  </si>
+  <si>
+    <t>I must be able to tap camera icon on store banner. I must be able to upload banner image. Image must update instantly. Image must maintain correct aspect ratio.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>edit my phone number or contact details</t>
+    </r>
+  </si>
+  <si>
+    <t>Customers can reach me correctly</t>
+  </si>
+  <si>
+    <t>I must be able to edit phone number. Updated number must validate country format (+61 for AU). Changes must be saved successfully. Success message must appear after saving. Invalid format must show error.</t>
+  </si>
+  <si>
+    <r>
+      <t>I want to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> access the Info section</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view information related to Micro2Move Business</t>
+  </si>
+  <si>
+    <t>When I tap “Info”, I must be redirected to Info screen. Info screen must contain platform-related information. I must be able to navigate back to Profile screen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>access the Community section</t>
+    </r>
+  </si>
+  <si>
+    <t>I can engage with Micro2Move community updates</t>
+  </si>
+  <si>
+    <t>When I tap “Community”, I must be redirected to Community screen. Community content must load dynamically. Back navigation must return me to Profile screen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I want to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>logout from the Supplier Portal</t>
+    </r>
+  </si>
+  <si>
+    <t>I can securely exit my account</t>
+  </si>
+  <si>
+    <t>When I tap Logout button: I must be logged out from the system. I must be redirected to Login screen. I must not be able to access dashboard without logging in again. Logout confirmation modal (optional enhancement).</t>
   </si>
 </sst>
 </file>
@@ -5901,7 +6139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5987,9 +6225,6 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -6024,6 +6259,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6316,11 +6560,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="2" customWidth="1"/>
     <col min="3" max="3" width="6.33203125" style="9" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="24" style="2" bestFit="1" customWidth="1"/>
@@ -6331,31 +6575,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="41" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -6365,8 +6609,8 @@
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -7760,184 +8004,321 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="37">
+      <c r="A74" s="36"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="36">
         <v>5.4</v>
       </c>
-      <c r="D74" s="38" t="s">
+      <c r="D74" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="E74" s="38" t="s">
+      <c r="E74" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="F74" s="38" t="s">
+      <c r="F74" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="G74" s="38" t="s">
+      <c r="G74" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="H74" s="38"/>
-    </row>
-    <row r="75" spans="1:9" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="35"/>
-      <c r="C75" s="35"/>
+      <c r="H74" s="37"/>
+    </row>
+    <row r="75" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="34"/>
+      <c r="C75" s="34"/>
     </row>
     <row r="76" spans="1:9" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="39">
+      <c r="A76" s="38">
         <v>6</v>
       </c>
-      <c r="B76" s="40" t="s">
+      <c r="B76" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="C76" s="39">
+      <c r="C76" s="38">
         <v>6.1</v>
       </c>
-      <c r="D76" s="40" t="s">
+      <c r="D76" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="E76" s="41" t="s">
+      <c r="E76" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="F76" s="41" t="s">
+      <c r="F76" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="G76" s="40" t="s">
+      <c r="G76" s="39" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="30"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="30">
+      <c r="A77" s="29"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="29">
         <v>6.2</v>
       </c>
-      <c r="D77" s="31" t="s">
+      <c r="D77" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="E77" s="31" t="s">
+      <c r="E77" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="F77" s="31" t="s">
+      <c r="F77" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="G77" s="31" t="s">
+      <c r="G77" s="30" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A78" s="30"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="31"/>
-      <c r="F78" s="31"/>
-      <c r="G78" s="31" t="s">
+      <c r="A78" s="29"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="32">
+      <c r="A79" s="31">
         <v>7</v>
       </c>
-      <c r="B79" s="33" t="s">
+      <c r="B79" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C79" s="31">
+        <v>7.1</v>
+      </c>
+      <c r="D79" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="C79" s="32">
-        <v>7.1</v>
-      </c>
-      <c r="D79" s="33" t="s">
+      <c r="E79" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="F79" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="E79" s="33" t="s">
+      <c r="G79" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="F79" s="33" t="s">
+    </row>
+    <row r="80" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="31"/>
+      <c r="B80" s="33"/>
+      <c r="C80" s="31"/>
+      <c r="D80" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="E80" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="F80" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="G80" s="33" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="31"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="31">
+        <v>7.2</v>
+      </c>
+      <c r="D81" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="G79" s="34" t="s">
+      <c r="E81" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="F81" s="33" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A80" s="32"/>
-      <c r="B80" s="34"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="33" t="s">
-        <v>242</v>
-      </c>
-      <c r="E80" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="F80" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="G80" s="34" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="32"/>
-      <c r="B81" s="34"/>
-      <c r="C81" s="32">
-        <v>7.2</v>
-      </c>
-      <c r="D81" s="34" t="s">
+      <c r="G81" s="33" t="s">
         <v>251</v>
       </c>
-      <c r="E81" s="33" t="s">
+    </row>
+    <row r="82" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="31"/>
+      <c r="B82" s="33"/>
+      <c r="C82" s="31"/>
+      <c r="D82" s="33"/>
+      <c r="E82" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="F82" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="G82" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="F81" s="34" t="s">
+    </row>
+    <row r="83" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="31"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="31"/>
+      <c r="D83" s="33"/>
+      <c r="E83" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="F83" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="G81" s="34" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="32"/>
-      <c r="B82" s="34"/>
-      <c r="C82" s="32"/>
-      <c r="D82" s="34"/>
-      <c r="E82" s="33" t="s">
+      <c r="G83" s="33" t="s">
         <v>255</v>
       </c>
-      <c r="F82" s="34" t="s">
+    </row>
+    <row r="84" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="31"/>
+      <c r="B84" s="33"/>
+      <c r="C84" s="31"/>
+      <c r="D84" s="33"/>
+      <c r="E84" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F84" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="G84" s="33" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="18">
+        <v>8</v>
+      </c>
+      <c r="B85" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="C85" s="18">
+        <v>8.1</v>
+      </c>
+      <c r="D85" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="G82" s="34" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A83" s="32"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="F83" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="G83" s="34" t="s">
+      <c r="E85" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="F85" s="19" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A84" s="32"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="34"/>
-      <c r="E84" s="34" t="s">
+      <c r="G85" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="F84" s="34" t="s">
+    </row>
+    <row r="86" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A86" s="18"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="18">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D86" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="F86" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="G84" s="34" t="s">
+      <c r="G86" s="19" t="s">
         <v>263</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A87" s="18"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="18">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="G87" s="19" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A88" s="18"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="18">
+        <v>8.4</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="G88" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="18"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="18">
+        <v>8.5</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="G89" s="19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="18"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="18">
+        <v>8.6</v>
+      </c>
+      <c r="D90" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E90" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G90" s="19" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A91" s="18"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="18">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D91" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="F91" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="G91" s="19" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
